--- a/Dim_Componentes_VSP.xlsx
+++ b/Dim_Componentes_VSP.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jcjua\Desktop\Tablas_Referencia_AT\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://saludcapitalgovco-my.sharepoint.com/personal/jcleon_saludcapital_gov_co/Documents/Tablas_Referencia_SDS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F720D04B-7165-412E-9F8E-C8C5050545E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{F720D04B-7165-412E-9F8E-C8C5050545E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A0933FA3-FBE7-4F22-B549-0A48B03E392D}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6625EA50-83D4-486A-A0BA-E91AF6E8BE6B}"/>
   </bookViews>
@@ -2769,7 +2769,7 @@
         <v>55</v>
       </c>
       <c r="E13" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F13" s="6" t="s">
         <v>41</v>

--- a/Dim_Componentes_VSP.xlsx
+++ b/Dim_Componentes_VSP.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://saludcapitalgovco-my.sharepoint.com/personal/jcleon_saludcapital_gov_co/Documents/Tablas_Referencia_SDS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{F720D04B-7165-412E-9F8E-C8C5050545E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A0933FA3-FBE7-4F22-B549-0A48B03E392D}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="13_ncr:1_{F720D04B-7165-412E-9F8E-C8C5050545E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{10EF48B1-1F5D-49B6-A0D4-845644109D3B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6625EA50-83D4-486A-A0BA-E91AF6E8BE6B}"/>
   </bookViews>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1296" uniqueCount="546">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1290" uniqueCount="556">
   <si>
     <t>Id_Global</t>
   </si>
@@ -668,9 +668,6 @@
     <t>4_1_1</t>
   </si>
   <si>
-    <t>Al revisar la base de datos la UPGD realiza notificacion semanal de casos confirmados nuevos de cáncer de mama y cuello uterino (7 Dias) de manera oportuna y con calidad.</t>
-  </si>
-  <si>
     <t>4_1</t>
   </si>
   <si>
@@ -680,1015 +677,1048 @@
     <t>10550</t>
   </si>
   <si>
-    <t>4_1_2</t>
-  </si>
-  <si>
-    <t>Al revisar la base de datos en las variables complementarias la UPGD garantiza  oportunidad (8 dias) en la toma de muestras y los resultados para cáncer de mama y cuello uterino.</t>
-  </si>
-  <si>
     <t>10560</t>
   </si>
   <si>
-    <t>4_1_3</t>
-  </si>
-  <si>
-    <t>Los casos de cáncer de cuello uterino y cáncer de mama cuentan con sus respectivas biopsias positivas compatibles con lo establecido con el protocolo del Instituto Nacional de Salud.</t>
-  </si>
-  <si>
     <t>10570</t>
   </si>
   <si>
-    <t>4_1_4</t>
-  </si>
-  <si>
-    <t>De acuerdo a la capacidad de la UPGD los casos notificados cuentan con fecha de inicio de tratamiento y este es posterior o igual a fecha de resultado de la biopsia.</t>
-  </si>
-  <si>
     <t>10580</t>
   </si>
   <si>
-    <t>4_1_5</t>
-  </si>
-  <si>
-    <t>La UPGD Garantiza el envío de la respuesta sobre los casos enviados por la Subred que han sido encontrados en la notificación SIANIEPS_Sivigila y garantiza que los casos que cumplen con definición operativa del evento se encuentran notificados.</t>
-  </si>
-  <si>
     <t>10590</t>
   </si>
   <si>
-    <t>4_1_6</t>
-  </si>
-  <si>
-    <t>La UPGD segun su capacidad instalada realiza seguimiento o establece acciones correctivas a casos notificados con fechas extremas entre  (fecha de resultado de biopsia y fecha de notificacion y/o fecha de inicio de tratamiento y fecha de resultado de la biopsia).</t>
-  </si>
-  <si>
     <t>10600</t>
   </si>
   <si>
     <t>5_1_1</t>
   </si>
   <si>
+    <t>5_1</t>
+  </si>
+  <si>
+    <t>SISVESO</t>
+  </si>
+  <si>
+    <t>10610</t>
+  </si>
+  <si>
+    <t>5_1_2</t>
+  </si>
+  <si>
+    <t>10620</t>
+  </si>
+  <si>
+    <t>5_2_1</t>
+  </si>
+  <si>
+    <t>Verificar que la UPGD cumple con el 100% de los compromisos establecidos en la visita anterior del SISVESO o de las acciones de mejora frente a los hallazgos encontrados en la anterior visita (cuando aplique). .</t>
+  </si>
+  <si>
+    <t>5_2</t>
+  </si>
+  <si>
+    <t>Compromisos y planes de mejoramiento</t>
+  </si>
+  <si>
+    <t>10630</t>
+  </si>
+  <si>
+    <t>5_3_1</t>
+  </si>
+  <si>
+    <t>Verificar que la totalidad de las variables de las fichas de notificación del SISVESO tomadas como muestra para evaluar este ítem, están diligenciadas con calidad e integralidad (de acuerdo con el instructivo de diligenciamiento de la ficha notificación).</t>
+  </si>
+  <si>
+    <t>5_3</t>
+  </si>
+  <si>
+    <t>10640</t>
+  </si>
+  <si>
+    <t>5_3_2</t>
+  </si>
+  <si>
+    <t>Verificar que las direcciones se encuentren registradas de acuerdo con el manual de nomenclatura y se encuentran correctamente georreferenciados los datos.</t>
+  </si>
+  <si>
+    <t>10650</t>
+  </si>
+  <si>
+    <t>5_3_3</t>
+  </si>
+  <si>
+    <t>Verificar que el odontólogo  que recibe la visita de monitoreo y seguimiento retroalimenta a los demás profesionales de la vigilancia del SISVESO sobre las fallas y/o fortalezas evidenciadas en el proceso de notificación.</t>
+  </si>
+  <si>
+    <t>10660</t>
+  </si>
+  <si>
+    <t>5_3_4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verificar que la UPGD cumple con el meta de fichas de notificación para la vigilancia del SISVESO, acordada con la Subred, (numero de fichas notificados con los eventos a vigilar) </t>
+  </si>
+  <si>
+    <t>10670</t>
+  </si>
+  <si>
+    <t>5_3_5</t>
+  </si>
+  <si>
+    <t>Verificar que la UPGD entrega o envía las fichas de notificación del SISVESO al correo oficial del subsistema de la subred de manera oportuna (corroborar el correo de envío).</t>
+  </si>
+  <si>
+    <t>10680</t>
+  </si>
+  <si>
+    <t>5_4_1</t>
+  </si>
+  <si>
+    <t>Verificar que la institución cuenta con instrumental  necesario  para la identificación de los eventos en salud oral.</t>
+  </si>
+  <si>
+    <t>5_4</t>
+  </si>
+  <si>
+    <t>Porcentaje de cumplimiento de proceso de VSP de la salud oral</t>
+  </si>
+  <si>
+    <t>10690</t>
+  </si>
+  <si>
+    <t>5_5_1</t>
+  </si>
+  <si>
+    <t>Verificar que las fichas de notificación de los eventos de salud oral son concordantes con lo registrado en la historia clínica (tomar la muestra del ítem 12% de cumplimiento en la notificación con calidad de eventos de interés en salud pública en salud oral).</t>
+  </si>
+  <si>
+    <t>5_5</t>
+  </si>
+  <si>
+    <t>10700</t>
+  </si>
+  <si>
+    <t>6_1_1</t>
+  </si>
+  <si>
+    <t>La UPGD cuenta con Talento Humano responsable de gestionar la identificación y notificación de eventos de interes para el  Subsistema SIVISTRA</t>
+  </si>
+  <si>
+    <t>6_1</t>
+  </si>
+  <si>
+    <t>SIVISTRA</t>
+  </si>
+  <si>
+    <t>10710</t>
+  </si>
+  <si>
+    <t>6_1_2</t>
+  </si>
+  <si>
+    <t>La UPGD cuenta con los recursos necesarios para cumplir con los procesos de notificación de eventos del Subsistema SIVISTRA (Equipo de computo - Internet, ficha de notificación SIVISTRA)</t>
+  </si>
+  <si>
+    <t>10720</t>
+  </si>
+  <si>
+    <t>6_2_1</t>
+  </si>
+  <si>
+    <t>La UPGD realiza inducción al talento humano nuevo y capacitación continua al personal sobre la operación del Subsistema de Vigilancia Epidemiologico SIVISTRA, al igual que  la retroalimentación de los casos intervenidos por VSP - Sivistra.</t>
+  </si>
+  <si>
+    <t>6_2</t>
+  </si>
+  <si>
+    <t>10730</t>
+  </si>
+  <si>
+    <t>6_2_2</t>
+  </si>
+  <si>
+    <t>Se realiza envío previo al desarrollo del seguimiento y monitoreo del acta de socialización o capacitación del subsistema del periodo evaluado.</t>
+  </si>
+  <si>
+    <t>10740</t>
+  </si>
+  <si>
+    <t>6_2_3</t>
+  </si>
+  <si>
+    <t>Se encuentra establecido el proceso de notificación de eventos de interés en Salud Pública que incluya eventos en salud y seguridad en el trabajo en la UPGD.</t>
+  </si>
+  <si>
+    <t>10750</t>
+  </si>
+  <si>
+    <t>6_3_1</t>
+  </si>
+  <si>
+    <t>LA UPGD cumple con el 100% de los compromisos establecidos en la visita anterior</t>
+  </si>
+  <si>
+    <t>6_3</t>
+  </si>
+  <si>
+    <t>10760</t>
+  </si>
+  <si>
+    <t>6_3_2</t>
+  </si>
+  <si>
+    <t>LA UPGD realiza seguimiento a los planes de mejoramiento y se evidencia los soportes (según aplique).</t>
+  </si>
+  <si>
+    <t>10770</t>
+  </si>
+  <si>
+    <t>6_4_1</t>
+  </si>
+  <si>
+    <t>La UPGD realiza notificación semanal al SIVISTRA(positiva o negativa).</t>
+  </si>
+  <si>
+    <t>6_4</t>
+  </si>
+  <si>
+    <t>10780</t>
+  </si>
+  <si>
+    <t>6_4_2</t>
+  </si>
+  <si>
+    <t>La UPGD presenta notificación positiva a SIVISTRA en el periodo verificado.</t>
+  </si>
+  <si>
+    <t>10790</t>
+  </si>
+  <si>
+    <t>6_4_3</t>
+  </si>
+  <si>
+    <t>10800</t>
+  </si>
+  <si>
+    <t>6_4_4</t>
+  </si>
+  <si>
+    <t>La Ficha de notificación se encuentra completamente diligenciado y cumple criterios de calidad.</t>
+  </si>
+  <si>
+    <t>10810</t>
+  </si>
+  <si>
+    <t>7_1_1</t>
+  </si>
+  <si>
+    <t>Verificar que el talento humano está capacitado en el proceso de notificación y apropiación de los conceptos definidos en el protocolo para el evento 342 vigente del INS y Anexo enfermedades huerfanas raras vigente del Minsalud.</t>
+  </si>
+  <si>
+    <t>7_1</t>
+  </si>
+  <si>
+    <t>EHR</t>
+  </si>
+  <si>
+    <t>10820</t>
+  </si>
+  <si>
+    <t>7_2_1</t>
+  </si>
+  <si>
+    <t>Verificar que la UPGD cumple con el 100% de los compromisos establecidos en la visita anterior.</t>
+  </si>
+  <si>
+    <t>7_2</t>
+  </si>
+  <si>
+    <t>10830</t>
+  </si>
+  <si>
+    <t>7_2_2</t>
+  </si>
+  <si>
+    <t>Verificar que la UPGD realiza seguimiento a los planes de mejoramiento y se evidencian los soportes (según aplique).</t>
+  </si>
+  <si>
+    <t>10840</t>
+  </si>
+  <si>
+    <t>7_3_1</t>
+  </si>
+  <si>
+    <t>Verificar que la UPGD reportó notificación negativa mensual del evento 342 durante el período evaluado a través de correo electrónico enviado al referente de evento de la subred máximo el tercer día hábil mes vencido.</t>
+  </si>
+  <si>
+    <t>7_3</t>
+  </si>
+  <si>
+    <t>10850</t>
+  </si>
+  <si>
+    <t>7_3_2</t>
+  </si>
+  <si>
+    <t>Verificar que la UPGD notifica y registra el evento 342 de manera adecuada según criterios del protocolo de vigilancia del INS y el Anexo protocolo enfermedades huerfanas raras vigentes en las siguientes variables el tipo de caso, código y nombre de la enfermedad, prueba de laboratorio (según aplique) y fecha de diagnóstico (fecha de resultado de la prueba), de acuerdo con la revisión de la base de datos del evento.</t>
+  </si>
+  <si>
+    <t>10860</t>
+  </si>
+  <si>
+    <t>7_3_3</t>
+  </si>
+  <si>
+    <t>Verificar de los casos confirmados por laboratorio, que estos cuenten con resultado o registro de procedimiento en la historia clínica confirmando la enfermedad huérfana - rara notificada de acuerdo con el Anexo protocolo enfermedades huerfanas raras vigente.</t>
+  </si>
+  <si>
+    <t>10870</t>
+  </si>
+  <si>
+    <t>7_3_4</t>
+  </si>
+  <si>
+    <t>Verificar la correlación entre la variable Personas en condición de discapacidad (cara A) y Otros grupos poblacionales (cara B) además de la solicitud (si aplica) del referente del evento de ajustar las anteriores variables de acuerdo con el cruce de RLCPD enviado desde el nivel central.</t>
+  </si>
+  <si>
+    <t>10880</t>
+  </si>
+  <si>
+    <t>7_3_5</t>
+  </si>
+  <si>
+    <t>Verificar que la UPGD notifica manera inmediata dentro de las primeras 24 horas a la fecha de confirmación del diagnóstico de la enfermedad huérfana - rara (se entiende como fecha de confirmación del diagnóstico la fecha de la consulta en la que el médico especialista confirma el diagnóstico), se tendrá en cuenta sólo para los casos diagnosticados durante el año de análisis.</t>
+  </si>
+  <si>
+    <t>10890</t>
+  </si>
+  <si>
+    <t>7_3_6</t>
+  </si>
+  <si>
+    <t>Verificar que la UPGD notifica el evento 342 como producto de la búsqueda en fuentes secundarias como el evento 215 - defectos congénitos (los casos que apliquen para la notificación de los dos eventos) y solicitud realizada como resultado del cruce con el evento 115 - cáncer infantil.</t>
+  </si>
+  <si>
+    <t>10900</t>
+  </si>
+  <si>
+    <t>7_3_7</t>
+  </si>
+  <si>
+    <t>Verificar en la base de datos del evento 342 se evidencie que la UPGD realiza el 100% de los ajustes solicitados por parte de la subred de manera oportuna y con calidad de aquellos casos que se identifica variables inconsistentes o con falta de integridad (según aplique).</t>
+  </si>
+  <si>
+    <t>10910</t>
+  </si>
+  <si>
+    <t>10920</t>
+  </si>
+  <si>
+    <t>Verificar en las UPGDs que reciben la solicitud de gestión de los casos de BAI desde las subredes se garantice la revisión de historias clínicas para la confirmación o descarte de la EHR y registro de la variable Nombre de la EAPB con la cual se gestionó el pago en el For_BAI_EHR.</t>
+  </si>
+  <si>
+    <t>10930</t>
+  </si>
+  <si>
+    <t>En las UPGDs que no reciban solicitud de gestión de BAI desde las subredes, se deberá verificar que se realice BAI a través de SIANIESP, teniendo en cuenta el histórico de EHR notificadas y de acuerdo con sus especialidades.</t>
+  </si>
+  <si>
+    <t>10940</t>
+  </si>
+  <si>
+    <t>8_1_1</t>
+  </si>
+  <si>
+    <t>La UPGD cuenta con talento humando responsable para la Vigilancia en Salud Publica de eventos bajo vigilancia en salud mental.</t>
+  </si>
+  <si>
+    <t>8_1</t>
+  </si>
+  <si>
+    <t>SIVIM</t>
+  </si>
+  <si>
+    <t>10950</t>
+  </si>
+  <si>
+    <t>8_1_2</t>
+  </si>
+  <si>
+    <t>El talento humano está capacitado en el proceso de Vigilancia en Salud Pública en los subsistemas de salud mental.</t>
+  </si>
+  <si>
+    <t>10960</t>
+  </si>
+  <si>
+    <t>8_1_3</t>
+  </si>
+  <si>
+    <t>La UPGD cuenta con lo formatos de notificación de los subistemas de salud mental y la infraestructura necesaria para cumplir con los procesos de Vigilancia en Salud Pública (Hardware, Software, Internet.</t>
+  </si>
+  <si>
+    <t>10970</t>
+  </si>
+  <si>
+    <t>8_2_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La UPGD cumple con el 100% de los compromisos establecidos en la visita anterior </t>
+  </si>
+  <si>
+    <t>8_2</t>
+  </si>
+  <si>
+    <t>10980</t>
+  </si>
+  <si>
+    <t>8_2_2</t>
+  </si>
+  <si>
+    <t>La UPGD realiza seguimiento a los planes de mejoramiento  y se evidencian las acciones soportadas que permiten subsanar el plan de mejora.</t>
+  </si>
+  <si>
+    <t>10990</t>
+  </si>
+  <si>
+    <t>8_3_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La UPGD informa oportunamente la necesidad de asistencia técnica en el manejo del fortmato de captura, flujo de notificación y definiciones operativas de cada subsistema y el comportamiento de la notificación. </t>
+  </si>
+  <si>
+    <t>8_3</t>
+  </si>
+  <si>
+    <t>11000</t>
+  </si>
+  <si>
+    <t>8_3_2</t>
+  </si>
+  <si>
+    <t>La UPGD informa oportunamente a la UPSS las fallas presentadas en el proceso de notificación, cierres temporales y/o Definitivos o  demás situaciones que alteran la notificación obligatoria de dentos de interes en salud publica.</t>
+  </si>
+  <si>
+    <t>11010</t>
+  </si>
+  <si>
+    <t>8_3_3</t>
+  </si>
+  <si>
+    <t>Se encuentra establecido el proceso de notificación de eventos de interes en salud Publica en la UPGD.</t>
+  </si>
+  <si>
+    <t>11020</t>
+  </si>
+  <si>
+    <t>8_4_1</t>
+  </si>
+  <si>
+    <t>La UPGD presenta silencio epidemiológico durante el periodo evaluado</t>
+  </si>
+  <si>
+    <t>8_4</t>
+  </si>
+  <si>
+    <t>11030</t>
+  </si>
+  <si>
+    <t>8_4_2</t>
+  </si>
+  <si>
+    <t>Todos los formatos de captura de datos, de la muestra representativa evaluadas están diligenciadas con calidad en la totalidad de las variables (Muestra de todos los eventos que la UPGD ha notificado)</t>
+  </si>
+  <si>
+    <t>11040</t>
+  </si>
+  <si>
+    <t>8_4_3</t>
+  </si>
+  <si>
+    <t>La UPGD presenta concordancia de la notificación entre la fecha de notificación, fecha de consulta y fecha del envio del evento a la Subred Integrada de Servicios de salud que corresponda.</t>
+  </si>
+  <si>
+    <t>11050</t>
+  </si>
+  <si>
+    <t>8_4_4</t>
+  </si>
+  <si>
+    <t>Al revisar la base de datos de la subred en relación a la UPGD  se evidencia que cumple con el proceso de notificación inmediata y rutinaria en los tiempos establecidos según subsistema de vigilancia y eventos prioritarios en salud mental de auerdo a lo establecido por el ente territorial.</t>
+  </si>
+  <si>
+    <t>11060</t>
+  </si>
+  <si>
+    <t>8_4_5</t>
+  </si>
+  <si>
+    <t>La UPGD registra las direcciones de acuerdo al manual de nomenclatura y se encuentran correctamente Georeferenciada.</t>
+  </si>
+  <si>
+    <t>11070</t>
+  </si>
+  <si>
+    <t>8_4_6</t>
+  </si>
+  <si>
+    <t>La UPGD realiza y envia BAI  de de los eventos de salud mental</t>
+  </si>
+  <si>
+    <t>11080</t>
+  </si>
+  <si>
+    <t>8_4_7</t>
+  </si>
+  <si>
+    <t>La UPGD garantiza que todos los casos encontrados en BAI se encuentran notificados.</t>
+  </si>
+  <si>
+    <t>11090</t>
+  </si>
+  <si>
+    <t>8_5_1</t>
+  </si>
+  <si>
+    <t>Concordancia entre los formatos de captura de datos y los registros digitados en la base de datos.</t>
+  </si>
+  <si>
+    <t>8_5</t>
+  </si>
+  <si>
+    <t>11100</t>
+  </si>
+  <si>
+    <t>9_1_1</t>
+  </si>
+  <si>
+    <t>9_1</t>
+  </si>
+  <si>
+    <t>SISVECOS</t>
+  </si>
+  <si>
+    <t>11110</t>
+  </si>
+  <si>
+    <t>9_1_2</t>
+  </si>
+  <si>
+    <t>11120</t>
+  </si>
+  <si>
+    <t>9_1_3</t>
+  </si>
+  <si>
+    <t>La UPGD cuenta con lo formatos de notificación de los subistemas de salud mental y la infraestructura necesaria para cumplir con los procesos de Vigilancia en Salud Pública (Hardware, Software, Internet)</t>
+  </si>
+  <si>
+    <t>11130</t>
+  </si>
+  <si>
+    <t>9_2_1</t>
+  </si>
+  <si>
+    <t>9_2</t>
+  </si>
+  <si>
+    <t>11140</t>
+  </si>
+  <si>
+    <t>9_2_2</t>
+  </si>
+  <si>
+    <t>11150</t>
+  </si>
+  <si>
+    <t>9_3_1</t>
+  </si>
+  <si>
+    <t>9_3</t>
+  </si>
+  <si>
+    <t>11160</t>
+  </si>
+  <si>
+    <t>9_3_2</t>
+  </si>
+  <si>
+    <t>11170</t>
+  </si>
+  <si>
+    <t>9_3_3</t>
+  </si>
+  <si>
+    <t>11180</t>
+  </si>
+  <si>
+    <t>9_4_1</t>
+  </si>
+  <si>
+    <t>9_4</t>
+  </si>
+  <si>
+    <t>11190</t>
+  </si>
+  <si>
+    <t>9_4_2</t>
+  </si>
+  <si>
+    <t>11200</t>
+  </si>
+  <si>
+    <t>9_4_3</t>
+  </si>
+  <si>
+    <t>11210</t>
+  </si>
+  <si>
+    <t>9_4_4</t>
+  </si>
+  <si>
+    <t>11220</t>
+  </si>
+  <si>
+    <t>9_4_5</t>
+  </si>
+  <si>
+    <t>11230</t>
+  </si>
+  <si>
+    <t>9_4_6</t>
+  </si>
+  <si>
+    <t>11240</t>
+  </si>
+  <si>
+    <t>9_4_7</t>
+  </si>
+  <si>
+    <t>11250</t>
+  </si>
+  <si>
+    <t>9_5_1</t>
+  </si>
+  <si>
+    <t>9_5</t>
+  </si>
+  <si>
+    <t>11260</t>
+  </si>
+  <si>
+    <t>10_1_1</t>
+  </si>
+  <si>
+    <t>10_1</t>
+  </si>
+  <si>
+    <t>SIVELCE</t>
+  </si>
+  <si>
+    <t>11270</t>
+  </si>
+  <si>
+    <t>10_1_2</t>
+  </si>
+  <si>
+    <t>11280</t>
+  </si>
+  <si>
+    <t>10_1_3</t>
+  </si>
+  <si>
+    <t>11290</t>
+  </si>
+  <si>
+    <t>10_2_1</t>
+  </si>
+  <si>
+    <t>10_2</t>
+  </si>
+  <si>
+    <t>11300</t>
+  </si>
+  <si>
+    <t>10_2_2</t>
+  </si>
+  <si>
+    <t>11310</t>
+  </si>
+  <si>
+    <t>10_3_1</t>
+  </si>
+  <si>
+    <t>10_3</t>
+  </si>
+  <si>
+    <t>11320</t>
+  </si>
+  <si>
+    <t>10_3_2</t>
+  </si>
+  <si>
+    <t>11330</t>
+  </si>
+  <si>
+    <t>10_3_3</t>
+  </si>
+  <si>
+    <t>11340</t>
+  </si>
+  <si>
+    <t>10_4_1</t>
+  </si>
+  <si>
+    <t>10_4</t>
+  </si>
+  <si>
+    <t>11350</t>
+  </si>
+  <si>
+    <t>10_4_2</t>
+  </si>
+  <si>
+    <t>11360</t>
+  </si>
+  <si>
+    <t>10_4_3</t>
+  </si>
+  <si>
+    <t>11370</t>
+  </si>
+  <si>
+    <t>10_4_4</t>
+  </si>
+  <si>
+    <t>11380</t>
+  </si>
+  <si>
+    <t>10_4_5</t>
+  </si>
+  <si>
+    <t>11390</t>
+  </si>
+  <si>
+    <t>10_4_6</t>
+  </si>
+  <si>
+    <t>11400</t>
+  </si>
+  <si>
+    <t>10_4_7</t>
+  </si>
+  <si>
+    <t>11410</t>
+  </si>
+  <si>
+    <t>10_5_1</t>
+  </si>
+  <si>
+    <t>10_5</t>
+  </si>
+  <si>
+    <t>11420</t>
+  </si>
+  <si>
+    <t>11_1_1</t>
+  </si>
+  <si>
+    <t>11_1</t>
+  </si>
+  <si>
+    <t>VESPA</t>
+  </si>
+  <si>
+    <t>11430</t>
+  </si>
+  <si>
+    <t>11_1_2</t>
+  </si>
+  <si>
+    <t>11440</t>
+  </si>
+  <si>
+    <t>11_1_3</t>
+  </si>
+  <si>
+    <t>11450</t>
+  </si>
+  <si>
+    <t>11_2_1</t>
+  </si>
+  <si>
+    <t>11_2</t>
+  </si>
+  <si>
+    <t>11460</t>
+  </si>
+  <si>
+    <t>11_2_2</t>
+  </si>
+  <si>
+    <t>11470</t>
+  </si>
+  <si>
+    <t>11_3_1</t>
+  </si>
+  <si>
+    <t>11_3</t>
+  </si>
+  <si>
+    <t>11480</t>
+  </si>
+  <si>
+    <t>11_3_2</t>
+  </si>
+  <si>
+    <t>11490</t>
+  </si>
+  <si>
+    <t>11_3_3</t>
+  </si>
+  <si>
+    <t>11500</t>
+  </si>
+  <si>
+    <t>11_4_1</t>
+  </si>
+  <si>
+    <t>11_4</t>
+  </si>
+  <si>
+    <t>11510</t>
+  </si>
+  <si>
+    <t>11_4_2</t>
+  </si>
+  <si>
+    <t>11520</t>
+  </si>
+  <si>
+    <t>11_4_3</t>
+  </si>
+  <si>
+    <t>11530</t>
+  </si>
+  <si>
+    <t>11_4_4</t>
+  </si>
+  <si>
+    <t>11540</t>
+  </si>
+  <si>
+    <t>11_4_5</t>
+  </si>
+  <si>
+    <t>11550</t>
+  </si>
+  <si>
+    <t>11560</t>
+  </si>
+  <si>
+    <t>11570</t>
+  </si>
+  <si>
+    <t>11_5_1</t>
+  </si>
+  <si>
+    <t>11_5</t>
+  </si>
+  <si>
+    <t>11580</t>
+  </si>
+  <si>
+    <t>12_1_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los profesionales involucrados en el manejo de la desnutrición aguda han recibido capacitación en resolución 2350 de 2020 y 2465 de 2016. </t>
+  </si>
+  <si>
+    <t>12_1</t>
+  </si>
+  <si>
+    <t>SISVAN</t>
+  </si>
+  <si>
+    <t>11590</t>
+  </si>
+  <si>
+    <t>12_1_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La institución cuenta con báscula de pie, pesabebés, tallímetro, infantómetro y cinta métrica para la toma de medidas antropométricas  y son los adecuados de acuerdo a la resolución 2465/2016, según el grupo vigilado por la UPGD. </t>
+  </si>
+  <si>
+    <t>11600</t>
+  </si>
+  <si>
+    <t>12_1_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los instrumentos utilizados para realizar la toma de medidas antropométricas, se encuentran en adecuada ubicación y estado; cuentan con hoja de vida y registro de calibración. </t>
+  </si>
+  <si>
+    <t>11610</t>
+  </si>
+  <si>
+    <t>12_2_1</t>
+  </si>
+  <si>
+    <t>Notifica los grupos objeto de vigilancia, de acuerdo con la naturaleza de la prestación del servicio de la institución.</t>
+  </si>
+  <si>
+    <t>12_2</t>
+  </si>
+  <si>
+    <t>11620</t>
+  </si>
+  <si>
+    <t>12_2_2</t>
+  </si>
+  <si>
+    <t>La UPGD presenta notificación con calidad de acuerdo al formato de captura de población objeto de vigilancia-precritica y resultados de los tableros de control de la notificación semanal</t>
+  </si>
+  <si>
+    <t>11630</t>
+  </si>
+  <si>
+    <t>12_2_3</t>
+  </si>
+  <si>
+    <t>La UPGD envía oportunamente la notificación de los componentes del SISVAN (Menores, Gestantes y Persona Mayor) de acuerdo con la naturaleza de la prestación del servicio de la institución.</t>
+  </si>
+  <si>
+    <t>11640</t>
+  </si>
+  <si>
+    <t>12_2_4</t>
+  </si>
+  <si>
+    <t>La UPGD envía oportunamente la concordancia de SISVAN y el evento 113,  definiendo el criterio(descartado o confirmado) de mas del 80% de los casos enviados por la subred</t>
+  </si>
+  <si>
+    <t>11650</t>
+  </si>
+  <si>
+    <t>12_3_1</t>
+  </si>
+  <si>
+    <t>Todos los casos notificados, de mayores de 6 meses, deben tener una de las 3 opciones que contempla  la ficha de notificación (positiva, negativa, no se realizó)</t>
+  </si>
+  <si>
+    <t>12_3</t>
+  </si>
+  <si>
+    <t>Reporte del resultado la prueba de apetito en el aplicativo SIVIGILA</t>
+  </si>
+  <si>
+    <t>12_4_1</t>
+  </si>
+  <si>
+    <t>La UPGD garantiza la inclusión de casos de Bajo Peso al Nacer en el programa canguro</t>
+  </si>
+  <si>
+    <t>12_4</t>
+  </si>
+  <si>
+    <t>Proporción de casos de BPN con activación de programa canguro</t>
+  </si>
+  <si>
+    <t>Puntaje_Esperado</t>
+  </si>
+  <si>
     <t xml:space="preserve">Verificar que la UPGD cuenta con el talento humano responsable para la vigilancia en salud pública de los eventos objeto de vigilancia salud oral. </t>
   </si>
   <si>
-    <t>5_1</t>
-  </si>
-  <si>
-    <t>SISVESO</t>
-  </si>
-  <si>
-    <t>10610</t>
-  </si>
-  <si>
-    <t>5_1_2</t>
-  </si>
-  <si>
     <t>Verificar que el talento humano está capacitado en el proceso de VSP de la salud oral y de notificación de los cuatro eventos de interés en salud oral caries (cavitacional y no cavitacional), gingivitis, periodontitis y edentulismo</t>
   </si>
   <si>
-    <t>10620</t>
-  </si>
-  <si>
-    <t>5_2_1</t>
-  </si>
-  <si>
-    <t>Verificar que la UPGD cumple con el 100% de los compromisos establecidos en la visita anterior del SISVESO o de las acciones de mejora frente a los hallazgos encontrados en la anterior visita (cuando aplique). .</t>
-  </si>
-  <si>
-    <t>5_2</t>
-  </si>
-  <si>
-    <t>Compromisos y planes de mejoramiento</t>
-  </si>
-  <si>
-    <t>10630</t>
-  </si>
-  <si>
-    <t>5_3_1</t>
-  </si>
-  <si>
-    <t>Verificar que la totalidad de las variables de las fichas de notificación del SISVESO tomadas como muestra para evaluar este ítem, están diligenciadas con calidad e integralidad (de acuerdo con el instructivo de diligenciamiento de la ficha notificación).</t>
-  </si>
-  <si>
-    <t>5_3</t>
-  </si>
-  <si>
-    <t>10640</t>
-  </si>
-  <si>
-    <t>5_3_2</t>
-  </si>
-  <si>
-    <t>Verificar que las direcciones se encuentren registradas de acuerdo con el manual de nomenclatura y se encuentran correctamente georreferenciados los datos.</t>
-  </si>
-  <si>
-    <t>10650</t>
-  </si>
-  <si>
-    <t>5_3_3</t>
-  </si>
-  <si>
-    <t>Verificar que el odontólogo  que recibe la visita de monitoreo y seguimiento retroalimenta a los demás profesionales de la vigilancia del SISVESO sobre las fallas y/o fortalezas evidenciadas en el proceso de notificación.</t>
-  </si>
-  <si>
-    <t>10660</t>
-  </si>
-  <si>
-    <t>5_3_4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verificar que la UPGD cumple con el meta de fichas de notificación para la vigilancia del SISVESO, acordada con la Subred, (numero de fichas notificados con los eventos a vigilar) </t>
-  </si>
-  <si>
-    <t>10670</t>
-  </si>
-  <si>
-    <t>5_3_5</t>
-  </si>
-  <si>
-    <t>Verificar que la UPGD entrega o envía las fichas de notificación del SISVESO al correo oficial del subsistema de la subred de manera oportuna (corroborar el correo de envío).</t>
-  </si>
-  <si>
-    <t>10680</t>
-  </si>
-  <si>
-    <t>5_4_1</t>
-  </si>
-  <si>
-    <t>Verificar que la institución cuenta con instrumental  necesario  para la identificación de los eventos en salud oral.</t>
-  </si>
-  <si>
-    <t>5_4</t>
-  </si>
-  <si>
-    <t>Porcentaje de cumplimiento de proceso de VSP de la salud oral</t>
-  </si>
-  <si>
-    <t>10690</t>
-  </si>
-  <si>
-    <t>5_5_1</t>
-  </si>
-  <si>
-    <t>Verificar que las fichas de notificación de los eventos de salud oral son concordantes con lo registrado en la historia clínica (tomar la muestra del ítem 12% de cumplimiento en la notificación con calidad de eventos de interés en salud pública en salud oral).</t>
-  </si>
-  <si>
-    <t>5_5</t>
-  </si>
-  <si>
-    <t>10700</t>
-  </si>
-  <si>
-    <t>6_1_1</t>
-  </si>
-  <si>
-    <t>La UPGD cuenta con Talento Humano responsable de gestionar la identificación y notificación de eventos de interes para el  Subsistema SIVISTRA</t>
-  </si>
-  <si>
-    <t>6_1</t>
-  </si>
-  <si>
-    <t>SIVISTRA</t>
-  </si>
-  <si>
-    <t>10710</t>
-  </si>
-  <si>
-    <t>6_1_2</t>
-  </si>
-  <si>
-    <t>La UPGD cuenta con los recursos necesarios para cumplir con los procesos de notificación de eventos del Subsistema SIVISTRA (Equipo de computo - Internet, ficha de notificación SIVISTRA)</t>
-  </si>
-  <si>
-    <t>10720</t>
-  </si>
-  <si>
-    <t>6_2_1</t>
-  </si>
-  <si>
-    <t>La UPGD realiza inducción al talento humano nuevo y capacitación continua al personal sobre la operación del Subsistema de Vigilancia Epidemiologico SIVISTRA, al igual que  la retroalimentación de los casos intervenidos por VSP - Sivistra.</t>
-  </si>
-  <si>
-    <t>6_2</t>
-  </si>
-  <si>
-    <t>10730</t>
-  </si>
-  <si>
-    <t>6_2_2</t>
-  </si>
-  <si>
-    <t>Se realiza envío previo al desarrollo del seguimiento y monitoreo del acta de socialización o capacitación del subsistema del periodo evaluado.</t>
-  </si>
-  <si>
-    <t>10740</t>
-  </si>
-  <si>
-    <t>6_2_3</t>
-  </si>
-  <si>
-    <t>Se encuentra establecido el proceso de notificación de eventos de interés en Salud Pública que incluya eventos en salud y seguridad en el trabajo en la UPGD.</t>
-  </si>
-  <si>
-    <t>10750</t>
-  </si>
-  <si>
-    <t>6_3_1</t>
-  </si>
-  <si>
-    <t>LA UPGD cumple con el 100% de los compromisos establecidos en la visita anterior</t>
-  </si>
-  <si>
-    <t>6_3</t>
-  </si>
-  <si>
-    <t>10760</t>
-  </si>
-  <si>
-    <t>6_3_2</t>
-  </si>
-  <si>
-    <t>LA UPGD realiza seguimiento a los planes de mejoramiento y se evidencia los soportes (según aplique).</t>
-  </si>
-  <si>
-    <t>10770</t>
-  </si>
-  <si>
-    <t>6_4_1</t>
-  </si>
-  <si>
-    <t>La UPGD realiza notificación semanal al SIVISTRA(positiva o negativa).</t>
-  </si>
-  <si>
-    <t>6_4</t>
-  </si>
-  <si>
-    <t>10780</t>
-  </si>
-  <si>
-    <t>6_4_2</t>
-  </si>
-  <si>
-    <t>La UPGD presenta notificación positiva a SIVISTRA en el periodo verificado.</t>
-  </si>
-  <si>
-    <t>10790</t>
-  </si>
-  <si>
-    <t>6_4_3</t>
-  </si>
-  <si>
-    <t>Búsqueda de los eventos de interés de Sivistra por medio de estrategias que permitan el rastreo de estos en otras fuentes de información en el periodo verificado.</t>
-  </si>
-  <si>
-    <t>10800</t>
-  </si>
-  <si>
-    <t>6_4_4</t>
-  </si>
-  <si>
-    <t>La Ficha de notificación se encuentra completamente diligenciado y cumple criterios de calidad.</t>
-  </si>
-  <si>
-    <t>10810</t>
-  </si>
-  <si>
-    <t>7_1_1</t>
-  </si>
-  <si>
-    <t>Verificar que el talento humano está capacitado en el proceso de notificación y apropiación de los conceptos definidos en el protocolo para el evento 342 vigente del INS y Anexo enfermedades huerfanas raras vigente del Minsalud.</t>
-  </si>
-  <si>
-    <t>7_1</t>
-  </si>
-  <si>
-    <t>EHR</t>
-  </si>
-  <si>
-    <t>10820</t>
-  </si>
-  <si>
-    <t>7_2_1</t>
-  </si>
-  <si>
-    <t>Verificar que la UPGD cumple con el 100% de los compromisos establecidos en la visita anterior.</t>
-  </si>
-  <si>
-    <t>7_2</t>
-  </si>
-  <si>
-    <t>10830</t>
-  </si>
-  <si>
-    <t>7_2_2</t>
-  </si>
-  <si>
-    <t>Verificar que la UPGD realiza seguimiento a los planes de mejoramiento y se evidencian los soportes (según aplique).</t>
-  </si>
-  <si>
-    <t>10840</t>
-  </si>
-  <si>
-    <t>7_3_1</t>
-  </si>
-  <si>
-    <t>Verificar que la UPGD reportó notificación negativa mensual del evento 342 durante el período evaluado a través de correo electrónico enviado al referente de evento de la subred máximo el tercer día hábil mes vencido.</t>
-  </si>
-  <si>
-    <t>7_3</t>
-  </si>
-  <si>
-    <t>10850</t>
-  </si>
-  <si>
-    <t>7_3_2</t>
-  </si>
-  <si>
-    <t>Verificar que la UPGD notifica y registra el evento 342 de manera adecuada según criterios del protocolo de vigilancia del INS y el Anexo protocolo enfermedades huerfanas raras vigentes en las siguientes variables el tipo de caso, código y nombre de la enfermedad, prueba de laboratorio (según aplique) y fecha de diagnóstico (fecha de resultado de la prueba), de acuerdo con la revisión de la base de datos del evento.</t>
-  </si>
-  <si>
-    <t>10860</t>
-  </si>
-  <si>
-    <t>7_3_3</t>
-  </si>
-  <si>
-    <t>Verificar de los casos confirmados por laboratorio, que estos cuenten con resultado o registro de procedimiento en la historia clínica confirmando la enfermedad huérfana - rara notificada de acuerdo con el Anexo protocolo enfermedades huerfanas raras vigente.</t>
-  </si>
-  <si>
-    <t>10870</t>
-  </si>
-  <si>
-    <t>7_3_4</t>
-  </si>
-  <si>
-    <t>Verificar la correlación entre la variable Personas en condición de discapacidad (cara A) y Otros grupos poblacionales (cara B) además de la solicitud (si aplica) del referente del evento de ajustar las anteriores variables de acuerdo con el cruce de RLCPD enviado desde el nivel central.</t>
-  </si>
-  <si>
-    <t>10880</t>
-  </si>
-  <si>
-    <t>7_3_5</t>
-  </si>
-  <si>
-    <t>Verificar que la UPGD notifica manera inmediata dentro de las primeras 24 horas a la fecha de confirmación del diagnóstico de la enfermedad huérfana - rara (se entiende como fecha de confirmación del diagnóstico la fecha de la consulta en la que el médico especialista confirma el diagnóstico), se tendrá en cuenta sólo para los casos diagnosticados durante el año de análisis.</t>
-  </si>
-  <si>
-    <t>10890</t>
-  </si>
-  <si>
-    <t>7_3_6</t>
-  </si>
-  <si>
-    <t>Verificar que la UPGD notifica el evento 342 como producto de la búsqueda en fuentes secundarias como el evento 215 - defectos congénitos (los casos que apliquen para la notificación de los dos eventos) y solicitud realizada como resultado del cruce con el evento 115 - cáncer infantil.</t>
-  </si>
-  <si>
-    <t>10900</t>
-  </si>
-  <si>
-    <t>7_3_7</t>
-  </si>
-  <si>
-    <t>Verificar en la base de datos del evento 342 se evidencie que la UPGD realiza el 100% de los ajustes solicitados por parte de la subred de manera oportuna y con calidad de aquellos casos que se identifica variables inconsistentes o con falta de integridad (según aplique).</t>
-  </si>
-  <si>
-    <t>10910</t>
-  </si>
-  <si>
-    <t>7_3_8</t>
-  </si>
-  <si>
-    <t>Verificar en las UPGDs que reciben la solicitud de gestión de los casos de BAI desde las subredes se garantice la notificación de todos los casos de enfermedades huérfanas - raras para el año epidemiológico en curso.</t>
-  </si>
-  <si>
-    <t>10920</t>
-  </si>
-  <si>
-    <t>7_3_9</t>
-  </si>
-  <si>
-    <t>Verificar en las UPGDs que reciben la solicitud de gestión de los casos de BAI desde las subredes se garantice la revisión de historias clínicas para la confirmación o descarte de la EHR y registro de la variable Nombre de la EAPB con la cual se gestionó el pago en el For_BAI_EHR.</t>
-  </si>
-  <si>
-    <t>10930</t>
-  </si>
-  <si>
-    <t>7_3_10</t>
-  </si>
-  <si>
-    <t>En las UPGDs que no reciban solicitud de gestión de BAI desde las subredes, se deberá verificar que se realice BAI a través de SIANIESP, teniendo en cuenta el histórico de EHR notificadas y de acuerdo con sus especialidades.</t>
-  </si>
-  <si>
-    <t>10940</t>
-  </si>
-  <si>
-    <t>8_1_1</t>
-  </si>
-  <si>
-    <t>La UPGD cuenta con talento humando responsable para la Vigilancia en Salud Publica de eventos bajo vigilancia en salud mental.</t>
-  </si>
-  <si>
-    <t>8_1</t>
-  </si>
-  <si>
-    <t>SIVIM</t>
-  </si>
-  <si>
-    <t>10950</t>
-  </si>
-  <si>
-    <t>8_1_2</t>
-  </si>
-  <si>
-    <t>El talento humano está capacitado en el proceso de Vigilancia en Salud Pública en los subsistemas de salud mental.</t>
-  </si>
-  <si>
-    <t>10960</t>
-  </si>
-  <si>
-    <t>8_1_3</t>
-  </si>
-  <si>
-    <t>La UPGD cuenta con lo formatos de notificación de los subistemas de salud mental y la infraestructura necesaria para cumplir con los procesos de Vigilancia en Salud Pública (Hardware, Software, Internet.</t>
-  </si>
-  <si>
-    <t>10970</t>
-  </si>
-  <si>
-    <t>8_2_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La UPGD cumple con el 100% de los compromisos establecidos en la visita anterior </t>
-  </si>
-  <si>
-    <t>8_2</t>
-  </si>
-  <si>
-    <t>10980</t>
-  </si>
-  <si>
-    <t>8_2_2</t>
-  </si>
-  <si>
-    <t>La UPGD realiza seguimiento a los planes de mejoramiento  y se evidencian las acciones soportadas que permiten subsanar el plan de mejora.</t>
-  </si>
-  <si>
-    <t>10990</t>
-  </si>
-  <si>
-    <t>8_3_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La UPGD informa oportunamente la necesidad de asistencia técnica en el manejo del fortmato de captura, flujo de notificación y definiciones operativas de cada subsistema y el comportamiento de la notificación. </t>
-  </si>
-  <si>
-    <t>8_3</t>
-  </si>
-  <si>
-    <t>11000</t>
-  </si>
-  <si>
-    <t>8_3_2</t>
-  </si>
-  <si>
-    <t>La UPGD informa oportunamente a la UPSS las fallas presentadas en el proceso de notificación, cierres temporales y/o Definitivos o  demás situaciones que alteran la notificación obligatoria de dentos de interes en salud publica.</t>
-  </si>
-  <si>
-    <t>11010</t>
-  </si>
-  <si>
-    <t>8_3_3</t>
-  </si>
-  <si>
-    <t>Se encuentra establecido el proceso de notificación de eventos de interes en salud Publica en la UPGD.</t>
-  </si>
-  <si>
-    <t>11020</t>
-  </si>
-  <si>
-    <t>8_4_1</t>
-  </si>
-  <si>
-    <t>La UPGD presenta silencio epidemiológico durante el periodo evaluado</t>
-  </si>
-  <si>
-    <t>8_4</t>
-  </si>
-  <si>
-    <t>11030</t>
-  </si>
-  <si>
-    <t>8_4_2</t>
-  </si>
-  <si>
-    <t>Todos los formatos de captura de datos, de la muestra representativa evaluadas están diligenciadas con calidad en la totalidad de las variables (Muestra de todos los eventos que la UPGD ha notificado)</t>
-  </si>
-  <si>
-    <t>11040</t>
-  </si>
-  <si>
-    <t>8_4_3</t>
-  </si>
-  <si>
-    <t>La UPGD presenta concordancia de la notificación entre la fecha de notificación, fecha de consulta y fecha del envio del evento a la Subred Integrada de Servicios de salud que corresponda.</t>
-  </si>
-  <si>
-    <t>11050</t>
-  </si>
-  <si>
-    <t>8_4_4</t>
-  </si>
-  <si>
-    <t>Al revisar la base de datos de la subred en relación a la UPGD  se evidencia que cumple con el proceso de notificación inmediata y rutinaria en los tiempos establecidos según subsistema de vigilancia y eventos prioritarios en salud mental de auerdo a lo establecido por el ente territorial.</t>
-  </si>
-  <si>
-    <t>11060</t>
-  </si>
-  <si>
-    <t>8_4_5</t>
-  </si>
-  <si>
-    <t>La UPGD registra las direcciones de acuerdo al manual de nomenclatura y se encuentran correctamente Georeferenciada.</t>
-  </si>
-  <si>
-    <t>11070</t>
-  </si>
-  <si>
-    <t>8_4_6</t>
-  </si>
-  <si>
-    <t>La UPGD realiza y envia BAI  de de los eventos de salud mental</t>
-  </si>
-  <si>
-    <t>11080</t>
-  </si>
-  <si>
-    <t>8_4_7</t>
-  </si>
-  <si>
-    <t>La UPGD garantiza que todos los casos encontrados en BAI se encuentran notificados.</t>
-  </si>
-  <si>
-    <t>11090</t>
-  </si>
-  <si>
-    <t>8_5_1</t>
-  </si>
-  <si>
-    <t>Concordancia entre los formatos de captura de datos y los registros digitados en la base de datos.</t>
-  </si>
-  <si>
-    <t>8_5</t>
-  </si>
-  <si>
-    <t>11100</t>
-  </si>
-  <si>
-    <t>9_1_1</t>
-  </si>
-  <si>
-    <t>9_1</t>
-  </si>
-  <si>
-    <t>SISVECOS</t>
-  </si>
-  <si>
-    <t>11110</t>
-  </si>
-  <si>
-    <t>9_1_2</t>
-  </si>
-  <si>
-    <t>11120</t>
-  </si>
-  <si>
-    <t>9_1_3</t>
-  </si>
-  <si>
-    <t>La UPGD cuenta con lo formatos de notificación de los subistemas de salud mental y la infraestructura necesaria para cumplir con los procesos de Vigilancia en Salud Pública (Hardware, Software, Internet)</t>
-  </si>
-  <si>
-    <t>11130</t>
-  </si>
-  <si>
-    <t>9_2_1</t>
-  </si>
-  <si>
-    <t>9_2</t>
-  </si>
-  <si>
-    <t>11140</t>
-  </si>
-  <si>
-    <t>9_2_2</t>
-  </si>
-  <si>
-    <t>11150</t>
-  </si>
-  <si>
-    <t>9_3_1</t>
-  </si>
-  <si>
-    <t>9_3</t>
-  </si>
-  <si>
-    <t>11160</t>
-  </si>
-  <si>
-    <t>9_3_2</t>
-  </si>
-  <si>
-    <t>11170</t>
-  </si>
-  <si>
-    <t>9_3_3</t>
-  </si>
-  <si>
-    <t>11180</t>
-  </si>
-  <si>
-    <t>9_4_1</t>
-  </si>
-  <si>
-    <t>9_4</t>
-  </si>
-  <si>
-    <t>11190</t>
-  </si>
-  <si>
-    <t>9_4_2</t>
-  </si>
-  <si>
-    <t>11200</t>
-  </si>
-  <si>
-    <t>9_4_3</t>
-  </si>
-  <si>
-    <t>11210</t>
-  </si>
-  <si>
-    <t>9_4_4</t>
-  </si>
-  <si>
-    <t>11220</t>
-  </si>
-  <si>
-    <t>9_4_5</t>
-  </si>
-  <si>
-    <t>11230</t>
-  </si>
-  <si>
-    <t>9_4_6</t>
-  </si>
-  <si>
-    <t>11240</t>
-  </si>
-  <si>
-    <t>9_4_7</t>
-  </si>
-  <si>
-    <t>11250</t>
-  </si>
-  <si>
-    <t>9_5_1</t>
-  </si>
-  <si>
-    <t>9_5</t>
-  </si>
-  <si>
-    <t>11260</t>
-  </si>
-  <si>
-    <t>10_1_1</t>
-  </si>
-  <si>
-    <t>10_1</t>
-  </si>
-  <si>
-    <t>SIVELCE</t>
-  </si>
-  <si>
-    <t>11270</t>
-  </si>
-  <si>
-    <t>10_1_2</t>
-  </si>
-  <si>
-    <t>11280</t>
-  </si>
-  <si>
-    <t>10_1_3</t>
-  </si>
-  <si>
-    <t>11290</t>
-  </si>
-  <si>
-    <t>10_2_1</t>
-  </si>
-  <si>
-    <t>10_2</t>
-  </si>
-  <si>
-    <t>11300</t>
-  </si>
-  <si>
-    <t>10_2_2</t>
-  </si>
-  <si>
-    <t>11310</t>
-  </si>
-  <si>
-    <t>10_3_1</t>
-  </si>
-  <si>
-    <t>10_3</t>
-  </si>
-  <si>
-    <t>11320</t>
-  </si>
-  <si>
-    <t>10_3_2</t>
-  </si>
-  <si>
-    <t>11330</t>
-  </si>
-  <si>
-    <t>10_3_3</t>
-  </si>
-  <si>
-    <t>11340</t>
-  </si>
-  <si>
-    <t>10_4_1</t>
-  </si>
-  <si>
-    <t>10_4</t>
-  </si>
-  <si>
-    <t>11350</t>
-  </si>
-  <si>
-    <t>10_4_2</t>
-  </si>
-  <si>
-    <t>11360</t>
-  </si>
-  <si>
-    <t>10_4_3</t>
-  </si>
-  <si>
-    <t>11370</t>
-  </si>
-  <si>
-    <t>10_4_4</t>
-  </si>
-  <si>
-    <t>11380</t>
-  </si>
-  <si>
-    <t>10_4_5</t>
-  </si>
-  <si>
-    <t>11390</t>
-  </si>
-  <si>
-    <t>10_4_6</t>
-  </si>
-  <si>
-    <t>11400</t>
-  </si>
-  <si>
-    <t>10_4_7</t>
-  </si>
-  <si>
-    <t>11410</t>
-  </si>
-  <si>
-    <t>10_5_1</t>
-  </si>
-  <si>
-    <t>10_5</t>
-  </si>
-  <si>
-    <t>11420</t>
-  </si>
-  <si>
-    <t>11_1_1</t>
-  </si>
-  <si>
-    <t>11_1</t>
-  </si>
-  <si>
-    <t>VESPA</t>
-  </si>
-  <si>
-    <t>11430</t>
-  </si>
-  <si>
-    <t>11_1_2</t>
-  </si>
-  <si>
-    <t>11440</t>
-  </si>
-  <si>
-    <t>11_1_3</t>
-  </si>
-  <si>
-    <t>11450</t>
-  </si>
-  <si>
-    <t>11_2_1</t>
-  </si>
-  <si>
-    <t>11_2</t>
-  </si>
-  <si>
-    <t>11460</t>
-  </si>
-  <si>
-    <t>11_2_2</t>
-  </si>
-  <si>
-    <t>11470</t>
-  </si>
-  <si>
-    <t>11_3_1</t>
-  </si>
-  <si>
-    <t>11_3</t>
-  </si>
-  <si>
-    <t>11480</t>
-  </si>
-  <si>
-    <t>11_3_2</t>
-  </si>
-  <si>
-    <t>11490</t>
-  </si>
-  <si>
-    <t>11_3_3</t>
-  </si>
-  <si>
-    <t>11500</t>
-  </si>
-  <si>
-    <t>11_4_1</t>
-  </si>
-  <si>
-    <t>11_4</t>
-  </si>
-  <si>
-    <t>11510</t>
-  </si>
-  <si>
-    <t>11_4_2</t>
-  </si>
-  <si>
-    <t>11520</t>
-  </si>
-  <si>
-    <t>11_4_3</t>
-  </si>
-  <si>
-    <t>11530</t>
-  </si>
-  <si>
-    <t>11_4_4</t>
-  </si>
-  <si>
-    <t>11540</t>
-  </si>
-  <si>
-    <t>11_4_5</t>
-  </si>
-  <si>
-    <t>11550</t>
-  </si>
-  <si>
-    <t>11_4_6</t>
-  </si>
-  <si>
-    <t>11560</t>
-  </si>
-  <si>
-    <t>11_4_7</t>
-  </si>
-  <si>
-    <t>11570</t>
-  </si>
-  <si>
-    <t>11_5_1</t>
-  </si>
-  <si>
-    <t>11_5</t>
-  </si>
-  <si>
-    <t>11580</t>
-  </si>
-  <si>
-    <t>12_1_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Los profesionales involucrados en el manejo de la desnutrición aguda han recibido capacitación en resolución 2350 de 2020 y 2465 de 2016. </t>
-  </si>
-  <si>
-    <t>12_1</t>
-  </si>
-  <si>
-    <t>SISVAN</t>
-  </si>
-  <si>
-    <t>11590</t>
-  </si>
-  <si>
-    <t>12_1_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La institución cuenta con báscula de pie, pesabebés, tallímetro, infantómetro y cinta métrica para la toma de medidas antropométricas  y son los adecuados de acuerdo a la resolución 2465/2016, según el grupo vigilado por la UPGD. </t>
-  </si>
-  <si>
-    <t>11600</t>
-  </si>
-  <si>
-    <t>12_1_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Los instrumentos utilizados para realizar la toma de medidas antropométricas, se encuentran en adecuada ubicación y estado; cuentan con hoja de vida y registro de calibración. </t>
-  </si>
-  <si>
-    <t>11610</t>
-  </si>
-  <si>
-    <t>12_2_1</t>
-  </si>
-  <si>
-    <t>Notifica los grupos objeto de vigilancia, de acuerdo con la naturaleza de la prestación del servicio de la institución.</t>
-  </si>
-  <si>
-    <t>12_2</t>
-  </si>
-  <si>
-    <t>11620</t>
-  </si>
-  <si>
-    <t>12_2_2</t>
-  </si>
-  <si>
-    <t>La UPGD presenta notificación con calidad de acuerdo al formato de captura de población objeto de vigilancia-precritica y resultados de los tableros de control de la notificación semanal</t>
-  </si>
-  <si>
-    <t>11630</t>
-  </si>
-  <si>
-    <t>12_2_3</t>
-  </si>
-  <si>
-    <t>La UPGD envía oportunamente la notificación de los componentes del SISVAN (Menores, Gestantes y Persona Mayor) de acuerdo con la naturaleza de la prestación del servicio de la institución.</t>
-  </si>
-  <si>
-    <t>11640</t>
-  </si>
-  <si>
-    <t>12_2_4</t>
-  </si>
-  <si>
-    <t>La UPGD envía oportunamente la concordancia de SISVAN y el evento 113,  definiendo el criterio(descartado o confirmado) de mas del 80% de los casos enviados por la subred</t>
-  </si>
-  <si>
-    <t>11650</t>
-  </si>
-  <si>
-    <t>12_3_1</t>
-  </si>
-  <si>
-    <t>Todos los casos notificados, de mayores de 6 meses, deben tener una de las 3 opciones que contempla  la ficha de notificación (positiva, negativa, no se realizó)</t>
-  </si>
-  <si>
-    <t>12_3</t>
-  </si>
-  <si>
-    <t>Reporte del resultado la prueba de apetito en el aplicativo SIVIGILA</t>
-  </si>
-  <si>
-    <t>11660</t>
-  </si>
-  <si>
-    <t>12_4_1</t>
-  </si>
-  <si>
-    <t>La UPGD garantiza la inclusión de casos de Bajo Peso al Nacer en el programa canguro</t>
-  </si>
-  <si>
-    <t>12_4</t>
-  </si>
-  <si>
-    <t>Proporción de casos de BPN con activación de programa canguro</t>
-  </si>
-  <si>
-    <t>Puntaje_Esperado</t>
+    <t>Búsqueda de los eventos de interés de Sivistra por medio de estrategias que permitan el rastreo de estos en otras fuentes de información en el periodo verificado, aplica cuando existe notificación negativa por dos semanas o más en un período epidemiológico.</t>
+  </si>
+  <si>
+    <t>7_4_1</t>
+  </si>
+  <si>
+    <t>Verificar en las UPGDs que reciben la solicitud de gestión de los casos de BAI desde las subredes, se garantice la notificación de todos los casos de enfermedades huérfanas - raras para el año epidemiológico en curso y verificar la respuesta oportuna.</t>
+  </si>
+  <si>
+    <t>7_4</t>
+  </si>
+  <si>
+    <t>Cumplimiento en la estrategia de búsqueda activa institucional</t>
+  </si>
+  <si>
+    <t>7_4_2</t>
+  </si>
+  <si>
+    <t>7_4_3</t>
+  </si>
+  <si>
+    <t>Se evaluará la capacidad de la UPGD para notificar oportunamente los casos confirmados de cáncer de mama y cuello uterino, tomando como referencia la diferencia en días calendario entre la fecha de resultado histopatológico confirmatorio y la fecha de notificación en SIVIGILA, mediante el cruce de estas variables en la base de datos de notificación, incluyendo datos básicos y complementarios. Se considerará que cumple cuando el 95% o más de los casos confirmados evaluados hayan sido notificados en un tiempo ≤7 días calendario; cumple parcialmente cuando la proporción se ubique entre el 80% y el 94,9%; cumple con oportunidad de mejora cuando se ubique entre el 70% y el 79,9%; y no cumple cuando sea menor al 70%, o cuando existan registros sin fechas válidas o con inconsistencias cronológicas que impidan calcular la oportunidad de notificación.</t>
+  </si>
+  <si>
+    <t>Oportunidad en la notificación</t>
+  </si>
+  <si>
+    <t>4_2_1</t>
+  </si>
+  <si>
+    <t>Se evaluará la oportunidad en la obtención del resultado histopatológico, medida como la diferencia en días calendario entre la fecha de toma de la biopsia y la fecha de disponibilidad del resultado diagnóstico, a partir de la verificación de estas variables en los soportes correspondientes y en la información registrada para el evento. Se considerará que cumple cuando el 80% o más de los casos evaluados se clasifiquen en oportunidad alta o media, y no se identifiquen inconsistencias en la calidad del dato, tales como fechas extremas, improbables o no soportadas documentalmente; y no cumple cuando menos del 80% de los casos evaluados se clasifiquen en oportunidad alta o media, o cuando se identifiquen inconsistencias en la calidad del dato que afecten la validez del análisis.</t>
+  </si>
+  <si>
+    <t>4_2</t>
+  </si>
+  <si>
+    <t>Oportunidad en la confirmación diagnóstica</t>
+  </si>
+  <si>
+    <t>4_3_1</t>
+  </si>
+  <si>
+    <t>Se evaluará la proporción de casos notificados que cuentan con soporte histopatológico válido y concordante con la definición operativa del evento Cód. 155, verificando la existencia del reporte histopatológico, su registro en el módulo de laboratorio y la correspondencia con el tipo de cáncer notificado. Se considerará que cumple cuando el 95% o más de los casos evaluados cuenten con soporte histopatológico válido y concordante; cumple parcialmente cuando la proporción se ubique entre el 80% y el 94,9%; cumple con oportunidad de mejora cuando se ubique entre el 70% y el 79,9%; y no cumple cuando sea menor al 70%, o cuando se identifiquen casos sin soporte histopatológico disponible, con soportes no válidos o con inconsistencias críticas entre el reporte de patología y la información registrada en SIVIGILA.</t>
+  </si>
+  <si>
+    <t>4_3</t>
+  </si>
+  <si>
+    <t>Calidad del  dato</t>
+  </si>
+  <si>
+    <t>4_3_2</t>
+  </si>
+  <si>
+    <t>Se verificará la consistencia lógica de la secuencia cronológica de las fechas registradas en el evento, con el propósito de validar la coherencia temporal del proceso de atención, confirmación diagnóstica y notificación en el sistema de vigilancia, a partir de la revisión de las variables FECHA_INICIO_SÍNTOMAS, FECHA_CONSULTA, FECHA_RESULTADO, FECHA_NOTIFICACIÓN y, cuando aplique, FECHA_INICIO_TRATAMIENTO. Se considerará que cumple cuando el 95% o más de los registros evaluados presenten una secuencia cronológica consistente; cumple parcialmente cuando la proporción se ubique entre el 80% y el 94,9%; cumple con oportunidad de mejora cuando se ubique entre el 70% y el 79,9%; y no cumple cuando sea menor al 70%, o cuando se identifiquen inconsistencias cronológicas críticas que afecten la validez del análisis del proceso de atención, confirmación diagnóstica o notificación en SIVIGILA.</t>
+  </si>
+  <si>
+    <t>4_3_3</t>
+  </si>
+  <si>
+    <t>Se evaluará la concordancia, completitud y consistencia lógica de las variables críticas registradas en Cara A de SIVIGILA, relacionadas con la identificación del caso, características sociodemográficas, afiliación al sistema de salud, aseguramiento y georreferenciación de residencia y ocurrencia. Esta verificación busca establecer la calidad del dato en la notificación del evento Cód. 155, así como la validez de la información requerida para la caracterización epidemiológica, el análisis territorial y el seguimiento de los casos notificados. Se considerará que cumple cuando el 95% o más de los registros evaluados presenten información completa, consistente y coherente; cumple parcialmente cuando la proporción se ubique entre el 80% y el 94,9%; cumple con oportunidad de mejora cuando se ubique entre el 70% y el 79,9%; y no cumple cuando sea menor al 70%, o cuando se identifiquen inconsistencias críticas que afecten la calidad del dato, la caracterización del caso o la validez de la información registrada.</t>
+  </si>
+  <si>
+    <t>4_4_1</t>
+  </si>
+  <si>
+    <t>Se evaluará la capacidad de la UPGD para gestionar los casos remitidos por la autoridad sanitaria local a través del reporte BAI_SIANIESP_SIVIGILA, verificando la revisión del caso, la emisión de respuesta en los tiempos establecidos, la confirmación del cumplimiento de la definición operativa del evento y la existencia de trazabilidad documental de la gestión realizada. Se considerará como cumple cuando el 100% de los casos remitidos por BAI_SIANIESP_SIVIGILA cuenten con revisión, respuesta oportuna, validación de la definición operativa y soporte documental de la gestión; y como no cumple cuando uno o más casos no cuenten con alguno de estos elementos.</t>
+  </si>
+  <si>
+    <t>4_4</t>
+  </si>
+  <si>
+    <t>Gestión de casos por BAI</t>
+  </si>
+  <si>
+    <t>4_5_1</t>
+  </si>
+  <si>
+    <t>Se evaluará la calidad, completitud, consistencia y trazabilidad del registro de la variable FECHA_INICIO_TRATAMIENTO, como variable crítica para el seguimiento del evento Cód. 155, verificando su concordancia con el inicio efectivo de tratamiento oncoespecífico, su correspondencia con los soportes clínicos disponibles y la gestión documentada por la UPGD en los casos sin dato registrado. Esta evaluación busca fortalecer la vigilancia epidemiológica del cáncer de mama y cuello uterino, mejorar la validez del indicador de oportunidad en el inicio del tratamiento definido en el protocolo del INS e identificar posibles brechas en la continuidad de la atención. El criterio se evaluará según la proporción de casos con registro consistente o evidencia documentada de gestión, clasificando el cumplimiento en los rangos establecidos para cumple, cumple parcialmente, cumple con oportunidad de mejora o no cumple.</t>
+  </si>
+  <si>
+    <t>4_5</t>
+  </si>
+  <si>
+    <t>Calidad del registro y gestión en fecha de inicio de tratamiento</t>
   </si>
 </sst>
 </file>
@@ -1750,10 +1780,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1787,12 +1818,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1808,10 +1833,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="4">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 5" xfId="1" xr:uid="{44A42900-4BC2-468B-BB4A-CF22FA88E96F}"/>
+    <cellStyle name="Normal 5 2" xfId="3" xr:uid="{24E8BFE2-65F6-41E2-8EC5-907390D292A2}"/>
     <cellStyle name="Normal_Hoja1" xfId="2" xr:uid="{1A187143-A490-4E05-95BC-482FF4D91F27}"/>
   </cellStyles>
   <dxfs count="11">
@@ -2058,18 +2090,18 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0E341BF0-FF04-477C-BDF9-C0D66BD64B45}" name="Dim_Componentes_SVSP" displayName="Dim_Componentes_SVSP" ref="A1:I167" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9">
-  <autoFilter ref="A1:I167" xr:uid="{69773485-FB11-499B-8D0F-46054A736DBA}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{80F83481-E46E-43DE-9D95-422AF1A554D6}" name="Dim_Componentes_SVSP3" displayName="Dim_Componentes_SVSP3" ref="A1:I166" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9">
+  <autoFilter ref="A1:I166" xr:uid="{80F83481-E46E-43DE-9D95-422AF1A554D6}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{9188A940-9D93-4AE6-8B1A-1C5BABEF1699}" name="Id_Global" dataDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{93CE9733-B67C-4B64-BC0A-F6B885E0C379}" name="Id_Componente" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{12F719C5-417D-4FAA-B665-B50057C4D7B1}" name="Componente" dataDxfId="6"/>
-    <tableColumn id="4" xr3:uid="{0F886AD4-5F74-4289-91BB-36B44DC507F0}" name="Orden" dataDxfId="5"/>
-    <tableColumn id="9" xr3:uid="{2FDB5B56-9DA6-4459-9D29-70248280AFB8}" name="Puntaje_Esperado" dataDxfId="4"/>
-    <tableColumn id="5" xr3:uid="{9F4AB3C1-56B2-40F8-B18C-4FEE0B30B466}" name="Id_Modulo" dataDxfId="3"/>
-    <tableColumn id="6" xr3:uid="{EFA2C5B6-DB35-431A-BFD5-D1F2FE337DBB}" name="Modulo" dataDxfId="2"/>
-    <tableColumn id="7" xr3:uid="{E2719B04-1AF8-41A3-950F-4E3C041AF0E6}" name="Id_Subsistema" dataDxfId="1"/>
-    <tableColumn id="8" xr3:uid="{D97194A3-71AD-43D7-991A-61C997EE6CDF}" name="Subsistema" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{B1A27102-7B7B-4FB0-8CDC-B37FBE546E73}" name="Id_Global" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{47BE095A-2C44-4FFF-9A17-D8E645121C23}" name="Id_Componente" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{9EBBD246-F1C2-49EA-BEA6-4F76A849EDA4}" name="Componente" dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{D7CD2DD6-37C9-4C2D-9E40-F3A4AC3E5565}" name="Orden" dataDxfId="5"/>
+    <tableColumn id="9" xr3:uid="{0BD9F86D-1369-408C-8E97-9CDD4CFDE664}" name="Puntaje_Esperado" dataDxfId="4"/>
+    <tableColumn id="5" xr3:uid="{AD6ADDDC-C7AB-49BE-B8FA-0004B3DA05F4}" name="Id_Modulo" dataDxfId="3"/>
+    <tableColumn id="6" xr3:uid="{AFEB9954-35FC-4C08-8DCF-F7A4A20AB368}" name="Modulo" dataDxfId="2"/>
+    <tableColumn id="7" xr3:uid="{D667DD16-2BD4-418B-8EF9-A0706A2BB1AF}" name="Id_Subsistema" dataDxfId="1"/>
+    <tableColumn id="8" xr3:uid="{62C6B465-ED76-4657-B381-6A8C8FC296CA}" name="Subsistema" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium19" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2393,15 +2425,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E66AA81A-5A75-47AB-8449-EABA6F85A7A5}">
   <sheetPr codeName="Hoja2"/>
-  <dimension ref="A1:I167"/>
+  <dimension ref="A1:I166"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.33203125" style="10" customWidth="1"/>
-    <col min="2" max="2" width="7.88671875" style="15" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="54.44140625" style="16" customWidth="1"/>
-    <col min="4" max="5" width="6.6640625" style="10" customWidth="1"/>
+    <col min="2" max="2" width="7.88671875" style="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="60.21875" style="14" customWidth="1"/>
+    <col min="4" max="4" width="5.77734375" style="10" customWidth="1"/>
+    <col min="5" max="5" width="6.6640625" style="10" customWidth="1"/>
     <col min="6" max="6" width="6" style="10" customWidth="1"/>
-    <col min="7" max="7" width="66.109375" style="17" customWidth="1"/>
+    <col min="7" max="7" width="66.109375" style="15" customWidth="1"/>
     <col min="8" max="8" width="6.33203125" style="10" customWidth="1"/>
     <col min="9" max="9" width="17.77734375" style="10" customWidth="1"/>
     <col min="10" max="16384" width="11.5546875" style="10"/>
@@ -2421,7 +2454,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>545</v>
+        <v>524</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
@@ -3981,94 +4014,94 @@
         <v>204</v>
       </c>
       <c r="C55" s="8" t="s">
+        <v>534</v>
+      </c>
+      <c r="D55" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E55" s="6">
+        <v>20</v>
+      </c>
+      <c r="F55" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="D55" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E55" s="6">
-        <v>25</v>
-      </c>
-      <c r="F55" s="6" t="s">
-        <v>206</v>
-      </c>
       <c r="G55" s="9" t="s">
-        <v>42</v>
+        <v>535</v>
       </c>
       <c r="H55" s="6" t="s">
         <v>37</v>
       </c>
       <c r="I55" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>209</v>
+        <v>536</v>
       </c>
       <c r="C56" s="8" t="s">
-        <v>210</v>
+        <v>537</v>
       </c>
       <c r="D56" s="6" t="s">
         <v>18</v>
       </c>
       <c r="E56" s="6">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F56" s="6" t="s">
-        <v>206</v>
+        <v>538</v>
       </c>
       <c r="G56" s="9" t="s">
-        <v>42</v>
+        <v>539</v>
       </c>
       <c r="H56" s="6" t="s">
         <v>37</v>
       </c>
       <c r="I56" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" s="6" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>212</v>
+        <v>540</v>
       </c>
       <c r="C57" s="8" t="s">
-        <v>213</v>
+        <v>541</v>
       </c>
       <c r="D57" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E57" s="6">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F57" s="6" t="s">
-        <v>206</v>
+        <v>542</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>42</v>
+        <v>543</v>
       </c>
       <c r="H57" s="6" t="s">
         <v>37</v>
       </c>
       <c r="I57" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" s="6" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>215</v>
+        <v>544</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>216</v>
+        <v>545</v>
       </c>
       <c r="D58" s="6" t="s">
         <v>37</v>
@@ -4077,123 +4110,123 @@
         <v>10</v>
       </c>
       <c r="F58" s="6" t="s">
-        <v>206</v>
+        <v>542</v>
       </c>
       <c r="G58" s="9" t="s">
-        <v>42</v>
+        <v>543</v>
       </c>
       <c r="H58" s="6" t="s">
         <v>37</v>
       </c>
       <c r="I58" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" s="6" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>218</v>
+        <v>546</v>
       </c>
       <c r="C59" s="8" t="s">
-        <v>219</v>
+        <v>547</v>
       </c>
       <c r="D59" s="6" t="s">
         <v>55</v>
       </c>
       <c r="E59" s="6">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F59" s="6" t="s">
-        <v>206</v>
+        <v>542</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>42</v>
+        <v>543</v>
       </c>
       <c r="H59" s="6" t="s">
         <v>37</v>
       </c>
       <c r="I59" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" s="6" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>221</v>
+        <v>548</v>
       </c>
       <c r="C60" s="8" t="s">
-        <v>222</v>
+        <v>549</v>
       </c>
       <c r="D60" s="6" t="s">
         <v>59</v>
       </c>
       <c r="E60" s="6">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F60" s="6" t="s">
-        <v>206</v>
+        <v>550</v>
       </c>
       <c r="G60" s="9" t="s">
-        <v>42</v>
+        <v>551</v>
       </c>
       <c r="H60" s="6" t="s">
         <v>37</v>
       </c>
       <c r="I60" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" s="6" t="s">
-        <v>223</v>
-      </c>
-      <c r="B61" s="11" t="s">
-        <v>224</v>
-      </c>
-      <c r="C61" s="12" t="s">
-        <v>225</v>
+        <v>212</v>
+      </c>
+      <c r="B61" s="7" t="s">
+        <v>552</v>
+      </c>
+      <c r="C61" s="8" t="s">
+        <v>553</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>11</v>
+        <v>63</v>
       </c>
       <c r="E61" s="6">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F61" s="6" t="s">
-        <v>226</v>
+        <v>554</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>13</v>
+        <v>555</v>
       </c>
       <c r="H61" s="6" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="I61" s="6" t="s">
-        <v>227</v>
+        <v>206</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" s="6" t="s">
-        <v>228</v>
-      </c>
-      <c r="B62" s="11" t="s">
-        <v>229</v>
-      </c>
-      <c r="C62" s="12" t="s">
-        <v>230</v>
+        <v>216</v>
+      </c>
+      <c r="B62" s="16" t="s">
+        <v>213</v>
+      </c>
+      <c r="C62" s="17" t="s">
+        <v>525</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E62" s="6">
         <v>5</v>
       </c>
       <c r="F62" s="6" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="G62" s="9" t="s">
         <v>13</v>
@@ -4202,85 +4235,85 @@
         <v>55</v>
       </c>
       <c r="I62" s="6" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" s="6" t="s">
-        <v>231</v>
-      </c>
-      <c r="B63" s="11" t="s">
-        <v>232</v>
-      </c>
-      <c r="C63" s="12" t="s">
-        <v>233</v>
+        <v>218</v>
+      </c>
+      <c r="B63" s="16" t="s">
+        <v>217</v>
+      </c>
+      <c r="C63" s="17" t="s">
+        <v>526</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E63" s="6">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F63" s="6" t="s">
-        <v>234</v>
+        <v>214</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>235</v>
+        <v>13</v>
       </c>
       <c r="H63" s="6" t="s">
         <v>55</v>
       </c>
       <c r="I63" s="6" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" s="6" t="s">
-        <v>236</v>
-      </c>
-      <c r="B64" s="11" t="s">
-        <v>237</v>
-      </c>
-      <c r="C64" s="12" t="s">
-        <v>238</v>
+        <v>223</v>
+      </c>
+      <c r="B64" s="16" t="s">
+        <v>219</v>
+      </c>
+      <c r="C64" s="17" t="s">
+        <v>220</v>
       </c>
       <c r="D64" s="6" t="s">
         <v>11</v>
       </c>
       <c r="E64" s="6">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F64" s="6" t="s">
-        <v>239</v>
+        <v>221</v>
       </c>
       <c r="G64" s="9" t="s">
-        <v>42</v>
+        <v>222</v>
       </c>
       <c r="H64" s="6" t="s">
         <v>55</v>
       </c>
       <c r="I64" s="6" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" s="6" t="s">
-        <v>240</v>
-      </c>
-      <c r="B65" s="11" t="s">
-        <v>241</v>
-      </c>
-      <c r="C65" s="12" t="s">
-        <v>242</v>
+        <v>227</v>
+      </c>
+      <c r="B65" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="C65" s="17" t="s">
+        <v>225</v>
       </c>
       <c r="D65" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E65" s="6">
         <v>18</v>
       </c>
-      <c r="E65" s="6">
-        <v>8</v>
-      </c>
       <c r="F65" s="6" t="s">
-        <v>239</v>
+        <v>226</v>
       </c>
       <c r="G65" s="9" t="s">
         <v>42</v>
@@ -4289,27 +4322,27 @@
         <v>55</v>
       </c>
       <c r="I65" s="6" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" s="6" t="s">
-        <v>243</v>
-      </c>
-      <c r="B66" s="11" t="s">
-        <v>244</v>
-      </c>
-      <c r="C66" s="12" t="s">
-        <v>245</v>
+        <v>230</v>
+      </c>
+      <c r="B66" s="16" t="s">
+        <v>228</v>
+      </c>
+      <c r="C66" s="17" t="s">
+        <v>229</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E66" s="6">
         <v>8</v>
       </c>
       <c r="F66" s="6" t="s">
-        <v>239</v>
+        <v>226</v>
       </c>
       <c r="G66" s="9" t="s">
         <v>42</v>
@@ -4318,27 +4351,27 @@
         <v>55</v>
       </c>
       <c r="I66" s="6" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67" s="6" t="s">
-        <v>246</v>
-      </c>
-      <c r="B67" s="11" t="s">
-        <v>247</v>
-      </c>
-      <c r="C67" s="12" t="s">
-        <v>248</v>
+        <v>233</v>
+      </c>
+      <c r="B67" s="16" t="s">
+        <v>231</v>
+      </c>
+      <c r="C67" s="17" t="s">
+        <v>232</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="E67" s="6">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F67" s="6" t="s">
-        <v>239</v>
+        <v>226</v>
       </c>
       <c r="G67" s="9" t="s">
         <v>42</v>
@@ -4347,27 +4380,27 @@
         <v>55</v>
       </c>
       <c r="I67" s="6" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68" s="6" t="s">
-        <v>249</v>
-      </c>
-      <c r="B68" s="11" t="s">
-        <v>250</v>
-      </c>
-      <c r="C68" s="12" t="s">
-        <v>251</v>
+        <v>236</v>
+      </c>
+      <c r="B68" s="16" t="s">
+        <v>234</v>
+      </c>
+      <c r="C68" s="17" t="s">
+        <v>235</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="E68" s="6">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F68" s="6" t="s">
-        <v>239</v>
+        <v>226</v>
       </c>
       <c r="G68" s="9" t="s">
         <v>42</v>
@@ -4376,114 +4409,114 @@
         <v>55</v>
       </c>
       <c r="I68" s="6" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="B69" s="11" t="s">
-        <v>253</v>
-      </c>
-      <c r="C69" s="12" t="s">
-        <v>254</v>
+        <v>239</v>
+      </c>
+      <c r="B69" s="16" t="s">
+        <v>237</v>
+      </c>
+      <c r="C69" s="17" t="s">
+        <v>238</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>11</v>
+        <v>55</v>
       </c>
       <c r="E69" s="6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F69" s="6" t="s">
-        <v>255</v>
+        <v>226</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>256</v>
+        <v>42</v>
       </c>
       <c r="H69" s="6" t="s">
         <v>55</v>
       </c>
       <c r="I69" s="6" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A70" s="6" t="s">
-        <v>257</v>
-      </c>
-      <c r="B70" s="11" t="s">
-        <v>258</v>
-      </c>
-      <c r="C70" s="12" t="s">
-        <v>259</v>
+        <v>244</v>
+      </c>
+      <c r="B70" s="16" t="s">
+        <v>240</v>
+      </c>
+      <c r="C70" s="17" t="s">
+        <v>241</v>
       </c>
       <c r="D70" s="6" t="s">
         <v>11</v>
       </c>
       <c r="E70" s="6">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F70" s="6" t="s">
-        <v>260</v>
+        <v>242</v>
       </c>
       <c r="G70" s="9" t="s">
-        <v>96</v>
+        <v>243</v>
       </c>
       <c r="H70" s="6" t="s">
         <v>55</v>
       </c>
       <c r="I70" s="6" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A71" s="6" t="s">
-        <v>261</v>
-      </c>
-      <c r="B71" s="7" t="s">
-        <v>262</v>
-      </c>
-      <c r="C71" s="8" t="s">
-        <v>263</v>
+        <v>248</v>
+      </c>
+      <c r="B71" s="16" t="s">
+        <v>245</v>
+      </c>
+      <c r="C71" s="17" t="s">
+        <v>246</v>
       </c>
       <c r="D71" s="6" t="s">
         <v>11</v>
       </c>
       <c r="E71" s="6">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F71" s="6" t="s">
-        <v>264</v>
+        <v>247</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>13</v>
+        <v>96</v>
       </c>
       <c r="H71" s="6" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="I71" s="6" t="s">
-        <v>265</v>
+        <v>215</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A72" s="6" t="s">
-        <v>266</v>
+        <v>253</v>
       </c>
       <c r="B72" s="7" t="s">
-        <v>267</v>
+        <v>249</v>
       </c>
       <c r="C72" s="8" t="s">
-        <v>268</v>
+        <v>250</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E72" s="6">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F72" s="6" t="s">
-        <v>264</v>
+        <v>251</v>
       </c>
       <c r="G72" s="9" t="s">
         <v>13</v>
@@ -4492,56 +4525,56 @@
         <v>59</v>
       </c>
       <c r="I72" s="6" t="s">
-        <v>265</v>
+        <v>252</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A73" s="6" t="s">
-        <v>269</v>
+        <v>256</v>
       </c>
       <c r="B73" s="7" t="s">
-        <v>270</v>
+        <v>254</v>
       </c>
       <c r="C73" s="8" t="s">
-        <v>271</v>
+        <v>255</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E73" s="6">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F73" s="6" t="s">
-        <v>272</v>
+        <v>251</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="H73" s="6" t="s">
         <v>59</v>
       </c>
       <c r="I73" s="6" t="s">
-        <v>265</v>
+        <v>252</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A74" s="6" t="s">
-        <v>273</v>
+        <v>260</v>
       </c>
       <c r="B74" s="7" t="s">
-        <v>274</v>
+        <v>257</v>
       </c>
       <c r="C74" s="8" t="s">
-        <v>275</v>
+        <v>258</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E74" s="6">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F74" s="6" t="s">
-        <v>272</v>
+        <v>259</v>
       </c>
       <c r="G74" s="9" t="s">
         <v>27</v>
@@ -4550,27 +4583,27 @@
         <v>59</v>
       </c>
       <c r="I74" s="6" t="s">
-        <v>265</v>
+        <v>252</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A75" s="6" t="s">
-        <v>276</v>
+        <v>263</v>
       </c>
       <c r="B75" s="7" t="s">
-        <v>277</v>
+        <v>261</v>
       </c>
       <c r="C75" s="8" t="s">
-        <v>278</v>
+        <v>262</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E75" s="6">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F75" s="6" t="s">
-        <v>272</v>
+        <v>259</v>
       </c>
       <c r="G75" s="9" t="s">
         <v>27</v>
@@ -4579,114 +4612,114 @@
         <v>59</v>
       </c>
       <c r="I75" s="6" t="s">
-        <v>265</v>
+        <v>252</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A76" s="6" t="s">
-        <v>279</v>
+        <v>266</v>
       </c>
       <c r="B76" s="7" t="s">
-        <v>280</v>
+        <v>264</v>
       </c>
       <c r="C76" s="8" t="s">
-        <v>281</v>
+        <v>265</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="E76" s="6">
         <v>10</v>
       </c>
       <c r="F76" s="6" t="s">
-        <v>282</v>
+        <v>259</v>
       </c>
       <c r="G76" s="9" t="s">
-        <v>235</v>
+        <v>27</v>
       </c>
       <c r="H76" s="6" t="s">
         <v>59</v>
       </c>
       <c r="I76" s="6" t="s">
-        <v>265</v>
+        <v>252</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A77" s="6" t="s">
-        <v>283</v>
+        <v>270</v>
       </c>
       <c r="B77" s="7" t="s">
-        <v>284</v>
+        <v>267</v>
       </c>
       <c r="C77" s="8" t="s">
-        <v>285</v>
+        <v>268</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E77" s="6">
         <v>10</v>
       </c>
       <c r="F77" s="6" t="s">
-        <v>282</v>
+        <v>269</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>235</v>
+        <v>222</v>
       </c>
       <c r="H77" s="6" t="s">
         <v>59</v>
       </c>
       <c r="I77" s="6" t="s">
-        <v>265</v>
+        <v>252</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A78" s="6" t="s">
-        <v>286</v>
+        <v>273</v>
       </c>
       <c r="B78" s="7" t="s">
-        <v>287</v>
+        <v>271</v>
       </c>
       <c r="C78" s="8" t="s">
-        <v>288</v>
+        <v>272</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E78" s="6">
         <v>10</v>
       </c>
       <c r="F78" s="6" t="s">
-        <v>289</v>
+        <v>269</v>
       </c>
       <c r="G78" s="9" t="s">
-        <v>42</v>
+        <v>222</v>
       </c>
       <c r="H78" s="6" t="s">
         <v>59</v>
       </c>
       <c r="I78" s="6" t="s">
-        <v>265</v>
+        <v>252</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A79" s="6" t="s">
-        <v>290</v>
+        <v>277</v>
       </c>
       <c r="B79" s="7" t="s">
-        <v>291</v>
+        <v>274</v>
       </c>
       <c r="C79" s="8" t="s">
-        <v>292</v>
+        <v>275</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E79" s="6">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F79" s="6" t="s">
-        <v>289</v>
+        <v>276</v>
       </c>
       <c r="G79" s="9" t="s">
         <v>42</v>
@@ -4695,27 +4728,27 @@
         <v>59</v>
       </c>
       <c r="I79" s="6" t="s">
-        <v>265</v>
+        <v>252</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A80" s="6" t="s">
-        <v>293</v>
+        <v>280</v>
       </c>
       <c r="B80" s="7" t="s">
-        <v>294</v>
+        <v>278</v>
       </c>
       <c r="C80" s="8" t="s">
-        <v>295</v>
+        <v>279</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E80" s="6">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F80" s="6" t="s">
-        <v>289</v>
+        <v>276</v>
       </c>
       <c r="G80" s="9" t="s">
         <v>42</v>
@@ -4724,27 +4757,27 @@
         <v>59</v>
       </c>
       <c r="I80" s="6" t="s">
-        <v>265</v>
+        <v>252</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A81" s="6" t="s">
-        <v>296</v>
+        <v>282</v>
       </c>
       <c r="B81" s="7" t="s">
-        <v>297</v>
+        <v>281</v>
       </c>
       <c r="C81" s="8" t="s">
-        <v>298</v>
+        <v>527</v>
       </c>
       <c r="D81" s="6" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="E81" s="6">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F81" s="6" t="s">
-        <v>289</v>
+        <v>276</v>
       </c>
       <c r="G81" s="9" t="s">
         <v>42</v>
@@ -4753,47 +4786,47 @@
         <v>59</v>
       </c>
       <c r="I81" s="6" t="s">
-        <v>265</v>
+        <v>252</v>
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A82" s="6" t="s">
-        <v>299</v>
+        <v>285</v>
       </c>
       <c r="B82" s="7" t="s">
-        <v>300</v>
+        <v>283</v>
       </c>
       <c r="C82" s="8" t="s">
-        <v>301</v>
+        <v>284</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="E82" s="6">
         <v>5</v>
       </c>
       <c r="F82" s="6" t="s">
-        <v>302</v>
+        <v>276</v>
       </c>
       <c r="G82" s="9" t="s">
-        <v>235</v>
+        <v>42</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="I82" s="6" t="s">
-        <v>303</v>
+        <v>252</v>
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A83" s="6" t="s">
-        <v>304</v>
+        <v>290</v>
       </c>
       <c r="B83" s="7" t="s">
-        <v>305</v>
+        <v>286</v>
       </c>
       <c r="C83" s="8" t="s">
-        <v>306</v>
+        <v>287</v>
       </c>
       <c r="D83" s="6" t="s">
         <v>11</v>
@@ -4802,94 +4835,94 @@
         <v>5</v>
       </c>
       <c r="F83" s="6" t="s">
-        <v>307</v>
+        <v>288</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>235</v>
+        <v>222</v>
       </c>
       <c r="H83" s="6" t="s">
         <v>63</v>
       </c>
       <c r="I83" s="6" t="s">
-        <v>303</v>
+        <v>289</v>
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A84" s="6" t="s">
-        <v>308</v>
+        <v>294</v>
       </c>
       <c r="B84" s="7" t="s">
-        <v>309</v>
+        <v>291</v>
       </c>
       <c r="C84" s="8" t="s">
-        <v>310</v>
+        <v>292</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E84" s="6">
         <v>5</v>
       </c>
       <c r="F84" s="6" t="s">
-        <v>307</v>
+        <v>293</v>
       </c>
       <c r="G84" s="9" t="s">
-        <v>235</v>
+        <v>222</v>
       </c>
       <c r="H84" s="6" t="s">
         <v>63</v>
       </c>
       <c r="I84" s="6" t="s">
-        <v>303</v>
+        <v>289</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A85" s="6" t="s">
-        <v>311</v>
+        <v>297</v>
       </c>
       <c r="B85" s="7" t="s">
-        <v>312</v>
+        <v>295</v>
       </c>
       <c r="C85" s="8" t="s">
-        <v>313</v>
+        <v>296</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E85" s="6">
         <v>5</v>
       </c>
       <c r="F85" s="6" t="s">
-        <v>314</v>
+        <v>293</v>
       </c>
       <c r="G85" s="9" t="s">
-        <v>42</v>
+        <v>222</v>
       </c>
       <c r="H85" s="6" t="s">
         <v>63</v>
       </c>
       <c r="I85" s="6" t="s">
-        <v>303</v>
+        <v>289</v>
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A86" s="6" t="s">
-        <v>315</v>
+        <v>301</v>
       </c>
       <c r="B86" s="7" t="s">
-        <v>316</v>
+        <v>298</v>
       </c>
       <c r="C86" s="8" t="s">
-        <v>317</v>
+        <v>299</v>
       </c>
       <c r="D86" s="6" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E86" s="6">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F86" s="6" t="s">
-        <v>314</v>
+        <v>300</v>
       </c>
       <c r="G86" s="9" t="s">
         <v>42</v>
@@ -4898,27 +4931,27 @@
         <v>63</v>
       </c>
       <c r="I86" s="6" t="s">
-        <v>303</v>
+        <v>289</v>
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A87" s="6" t="s">
-        <v>318</v>
+        <v>304</v>
       </c>
       <c r="B87" s="7" t="s">
-        <v>319</v>
+        <v>302</v>
       </c>
       <c r="C87" s="8" t="s">
-        <v>320</v>
+        <v>303</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E87" s="6">
         <v>15</v>
       </c>
       <c r="F87" s="6" t="s">
-        <v>314</v>
+        <v>300</v>
       </c>
       <c r="G87" s="9" t="s">
         <v>42</v>
@@ -4927,27 +4960,27 @@
         <v>63</v>
       </c>
       <c r="I87" s="6" t="s">
-        <v>303</v>
+        <v>289</v>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A88" s="6" t="s">
-        <v>321</v>
+        <v>307</v>
       </c>
       <c r="B88" s="7" t="s">
-        <v>322</v>
+        <v>305</v>
       </c>
       <c r="C88" s="8" t="s">
-        <v>323</v>
+        <v>306</v>
       </c>
       <c r="D88" s="6" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="E88" s="6">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F88" s="6" t="s">
-        <v>314</v>
+        <v>300</v>
       </c>
       <c r="G88" s="9" t="s">
         <v>42</v>
@@ -4956,27 +4989,27 @@
         <v>63</v>
       </c>
       <c r="I88" s="6" t="s">
-        <v>303</v>
+        <v>289</v>
       </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A89" s="6" t="s">
-        <v>324</v>
+        <v>310</v>
       </c>
       <c r="B89" s="7" t="s">
-        <v>325</v>
+        <v>308</v>
       </c>
       <c r="C89" s="8" t="s">
-        <v>326</v>
+        <v>309</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="E89" s="6">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F89" s="6" t="s">
-        <v>314</v>
+        <v>300</v>
       </c>
       <c r="G89" s="9" t="s">
         <v>42</v>
@@ -4985,27 +5018,27 @@
         <v>63</v>
       </c>
       <c r="I89" s="6" t="s">
-        <v>303</v>
+        <v>289</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A90" s="6" t="s">
-        <v>327</v>
+        <v>313</v>
       </c>
       <c r="B90" s="7" t="s">
-        <v>328</v>
+        <v>311</v>
       </c>
       <c r="C90" s="8" t="s">
-        <v>329</v>
+        <v>312</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E90" s="6">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F90" s="6" t="s">
-        <v>314</v>
+        <v>300</v>
       </c>
       <c r="G90" s="9" t="s">
         <v>42</v>
@@ -5014,27 +5047,27 @@
         <v>63</v>
       </c>
       <c r="I90" s="6" t="s">
-        <v>303</v>
+        <v>289</v>
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A91" s="6" t="s">
-        <v>330</v>
+        <v>316</v>
       </c>
       <c r="B91" s="7" t="s">
-        <v>331</v>
+        <v>314</v>
       </c>
       <c r="C91" s="8" t="s">
-        <v>332</v>
+        <v>315</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E91" s="6">
         <v>9</v>
       </c>
       <c r="F91" s="6" t="s">
-        <v>314</v>
+        <v>300</v>
       </c>
       <c r="G91" s="9" t="s">
         <v>42</v>
@@ -5043,27 +5076,27 @@
         <v>63</v>
       </c>
       <c r="I91" s="6" t="s">
-        <v>303</v>
+        <v>289</v>
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A92" s="6" t="s">
-        <v>333</v>
+        <v>319</v>
       </c>
       <c r="B92" s="7" t="s">
-        <v>334</v>
+        <v>317</v>
       </c>
       <c r="C92" s="8" t="s">
-        <v>335</v>
+        <v>318</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="E92" s="6">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F92" s="6" t="s">
-        <v>314</v>
+        <v>300</v>
       </c>
       <c r="G92" s="9" t="s">
         <v>42</v>
@@ -5072,114 +5105,114 @@
         <v>63</v>
       </c>
       <c r="I92" s="6" t="s">
-        <v>303</v>
+        <v>289</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A93" s="6" t="s">
-        <v>336</v>
+        <v>320</v>
       </c>
       <c r="B93" s="7" t="s">
-        <v>337</v>
+        <v>528</v>
       </c>
       <c r="C93" s="8" t="s">
-        <v>338</v>
+        <v>529</v>
       </c>
       <c r="D93" s="6" t="s">
-        <v>71</v>
+        <v>11</v>
       </c>
       <c r="E93" s="6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F93" s="6" t="s">
-        <v>314</v>
+        <v>530</v>
       </c>
       <c r="G93" s="9" t="s">
-        <v>42</v>
+        <v>531</v>
       </c>
       <c r="H93" s="6" t="s">
         <v>63</v>
       </c>
       <c r="I93" s="6" t="s">
-        <v>303</v>
+        <v>289</v>
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A94" s="6" t="s">
-        <v>339</v>
+        <v>322</v>
       </c>
       <c r="B94" s="7" t="s">
-        <v>340</v>
+        <v>532</v>
       </c>
       <c r="C94" s="8" t="s">
-        <v>341</v>
+        <v>321</v>
       </c>
       <c r="D94" s="6" t="s">
-        <v>75</v>
+        <v>18</v>
       </c>
       <c r="E94" s="6">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F94" s="6" t="s">
-        <v>314</v>
+        <v>530</v>
       </c>
       <c r="G94" s="9" t="s">
-        <v>42</v>
+        <v>531</v>
       </c>
       <c r="H94" s="6" t="s">
         <v>63</v>
       </c>
       <c r="I94" s="6" t="s">
-        <v>303</v>
+        <v>289</v>
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A95" s="6" t="s">
-        <v>342</v>
-      </c>
-      <c r="B95" s="13" t="s">
-        <v>343</v>
-      </c>
-      <c r="C95" s="14" t="s">
-        <v>344</v>
+        <v>324</v>
+      </c>
+      <c r="B95" s="7" t="s">
+        <v>533</v>
+      </c>
+      <c r="C95" s="8" t="s">
+        <v>323</v>
       </c>
       <c r="D95" s="6" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="E95" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F95" s="6" t="s">
-        <v>345</v>
+        <v>530</v>
       </c>
       <c r="G95" s="9" t="s">
-        <v>27</v>
+        <v>531</v>
       </c>
       <c r="H95" s="6" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="I95" s="6" t="s">
-        <v>346</v>
+        <v>289</v>
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A96" s="6" t="s">
-        <v>347</v>
-      </c>
-      <c r="B96" s="13" t="s">
-        <v>348</v>
-      </c>
-      <c r="C96" s="14" t="s">
-        <v>349</v>
+        <v>329</v>
+      </c>
+      <c r="B96" s="11" t="s">
+        <v>325</v>
+      </c>
+      <c r="C96" s="12" t="s">
+        <v>326</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E96" s="6">
         <v>2</v>
       </c>
       <c r="F96" s="6" t="s">
-        <v>345</v>
+        <v>327</v>
       </c>
       <c r="G96" s="9" t="s">
         <v>27</v>
@@ -5188,27 +5221,27 @@
         <v>67</v>
       </c>
       <c r="I96" s="6" t="s">
-        <v>346</v>
+        <v>328</v>
       </c>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A97" s="6" t="s">
-        <v>350</v>
-      </c>
-      <c r="B97" s="13" t="s">
-        <v>351</v>
-      </c>
-      <c r="C97" s="14" t="s">
-        <v>352</v>
+        <v>332</v>
+      </c>
+      <c r="B97" s="11" t="s">
+        <v>330</v>
+      </c>
+      <c r="C97" s="12" t="s">
+        <v>331</v>
       </c>
       <c r="D97" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E97" s="6">
         <v>2</v>
       </c>
       <c r="F97" s="6" t="s">
-        <v>345</v>
+        <v>327</v>
       </c>
       <c r="G97" s="9" t="s">
         <v>27</v>
@@ -5217,27 +5250,27 @@
         <v>67</v>
       </c>
       <c r="I97" s="6" t="s">
-        <v>346</v>
+        <v>328</v>
       </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A98" s="6" t="s">
-        <v>353</v>
-      </c>
-      <c r="B98" s="13" t="s">
-        <v>354</v>
-      </c>
-      <c r="C98" s="14" t="s">
-        <v>355</v>
+        <v>335</v>
+      </c>
+      <c r="B98" s="11" t="s">
+        <v>333</v>
+      </c>
+      <c r="C98" s="12" t="s">
+        <v>334</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="E98" s="6">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F98" s="6" t="s">
-        <v>356</v>
+        <v>327</v>
       </c>
       <c r="G98" s="9" t="s">
         <v>27</v>
@@ -5246,27 +5279,27 @@
         <v>67</v>
       </c>
       <c r="I98" s="6" t="s">
-        <v>346</v>
+        <v>328</v>
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A99" s="6" t="s">
-        <v>357</v>
-      </c>
-      <c r="B99" s="13" t="s">
-        <v>358</v>
-      </c>
-      <c r="C99" s="14" t="s">
-        <v>359</v>
+        <v>339</v>
+      </c>
+      <c r="B99" s="11" t="s">
+        <v>336</v>
+      </c>
+      <c r="C99" s="12" t="s">
+        <v>337</v>
       </c>
       <c r="D99" s="6" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E99" s="6">
         <v>8</v>
       </c>
       <c r="F99" s="6" t="s">
-        <v>356</v>
+        <v>338</v>
       </c>
       <c r="G99" s="9" t="s">
         <v>27</v>
@@ -5275,27 +5308,27 @@
         <v>67</v>
       </c>
       <c r="I99" s="6" t="s">
-        <v>346</v>
+        <v>328</v>
       </c>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A100" s="6" t="s">
-        <v>360</v>
-      </c>
-      <c r="B100" s="13" t="s">
-        <v>361</v>
-      </c>
-      <c r="C100" s="14" t="s">
-        <v>362</v>
+        <v>342</v>
+      </c>
+      <c r="B100" s="11" t="s">
+        <v>340</v>
+      </c>
+      <c r="C100" s="12" t="s">
+        <v>341</v>
       </c>
       <c r="D100" s="6" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E100" s="6">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F100" s="6" t="s">
-        <v>363</v>
+        <v>338</v>
       </c>
       <c r="G100" s="9" t="s">
         <v>27</v>
@@ -5304,27 +5337,27 @@
         <v>67</v>
       </c>
       <c r="I100" s="6" t="s">
-        <v>346</v>
+        <v>328</v>
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A101" s="6" t="s">
-        <v>364</v>
-      </c>
-      <c r="B101" s="13" t="s">
-        <v>365</v>
-      </c>
-      <c r="C101" s="14" t="s">
-        <v>366</v>
+        <v>346</v>
+      </c>
+      <c r="B101" s="11" t="s">
+        <v>343</v>
+      </c>
+      <c r="C101" s="12" t="s">
+        <v>344</v>
       </c>
       <c r="D101" s="6" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E101" s="6">
         <v>4</v>
       </c>
       <c r="F101" s="6" t="s">
-        <v>363</v>
+        <v>345</v>
       </c>
       <c r="G101" s="9" t="s">
         <v>27</v>
@@ -5333,27 +5366,27 @@
         <v>67</v>
       </c>
       <c r="I101" s="6" t="s">
-        <v>346</v>
+        <v>328</v>
       </c>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A102" s="6" t="s">
-        <v>367</v>
-      </c>
-      <c r="B102" s="13" t="s">
-        <v>368</v>
-      </c>
-      <c r="C102" s="14" t="s">
-        <v>369</v>
+        <v>349</v>
+      </c>
+      <c r="B102" s="11" t="s">
+        <v>347</v>
+      </c>
+      <c r="C102" s="12" t="s">
+        <v>348</v>
       </c>
       <c r="D102" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E102" s="6">
         <v>4</v>
       </c>
       <c r="F102" s="6" t="s">
-        <v>363</v>
+        <v>345</v>
       </c>
       <c r="G102" s="9" t="s">
         <v>27</v>
@@ -5362,56 +5395,56 @@
         <v>67</v>
       </c>
       <c r="I102" s="6" t="s">
-        <v>346</v>
+        <v>328</v>
       </c>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A103" s="6" t="s">
-        <v>370</v>
-      </c>
-      <c r="B103" s="13" t="s">
-        <v>371</v>
-      </c>
-      <c r="C103" s="14" t="s">
-        <v>372</v>
+        <v>352</v>
+      </c>
+      <c r="B103" s="11" t="s">
+        <v>350</v>
+      </c>
+      <c r="C103" s="12" t="s">
+        <v>351</v>
       </c>
       <c r="D103" s="6" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="E103" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F103" s="6" t="s">
-        <v>373</v>
+        <v>345</v>
       </c>
       <c r="G103" s="9" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="H103" s="6" t="s">
         <v>67</v>
       </c>
       <c r="I103" s="6" t="s">
-        <v>346</v>
+        <v>328</v>
       </c>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A104" s="6" t="s">
-        <v>374</v>
-      </c>
-      <c r="B104" s="13" t="s">
-        <v>375</v>
-      </c>
-      <c r="C104" s="14" t="s">
-        <v>376</v>
+        <v>356</v>
+      </c>
+      <c r="B104" s="11" t="s">
+        <v>353</v>
+      </c>
+      <c r="C104" s="12" t="s">
+        <v>354</v>
       </c>
       <c r="D104" s="6" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E104" s="6">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F104" s="6" t="s">
-        <v>373</v>
+        <v>355</v>
       </c>
       <c r="G104" s="9" t="s">
         <v>42</v>
@@ -5420,27 +5453,27 @@
         <v>67</v>
       </c>
       <c r="I104" s="6" t="s">
-        <v>346</v>
+        <v>328</v>
       </c>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A105" s="6" t="s">
-        <v>377</v>
-      </c>
-      <c r="B105" s="13" t="s">
-        <v>378</v>
-      </c>
-      <c r="C105" s="14" t="s">
-        <v>379</v>
+        <v>359</v>
+      </c>
+      <c r="B105" s="11" t="s">
+        <v>357</v>
+      </c>
+      <c r="C105" s="12" t="s">
+        <v>358</v>
       </c>
       <c r="D105" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E105" s="6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F105" s="6" t="s">
-        <v>373</v>
+        <v>355</v>
       </c>
       <c r="G105" s="9" t="s">
         <v>42</v>
@@ -5449,27 +5482,27 @@
         <v>67</v>
       </c>
       <c r="I105" s="6" t="s">
-        <v>346</v>
+        <v>328</v>
       </c>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A106" s="6" t="s">
-        <v>380</v>
-      </c>
-      <c r="B106" s="13" t="s">
-        <v>381</v>
-      </c>
-      <c r="C106" s="14" t="s">
-        <v>382</v>
+        <v>362</v>
+      </c>
+      <c r="B106" s="11" t="s">
+        <v>360</v>
+      </c>
+      <c r="C106" s="12" t="s">
+        <v>361</v>
       </c>
       <c r="D106" s="6" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="E106" s="6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F106" s="6" t="s">
-        <v>373</v>
+        <v>355</v>
       </c>
       <c r="G106" s="9" t="s">
         <v>42</v>
@@ -5478,27 +5511,27 @@
         <v>67</v>
       </c>
       <c r="I106" s="6" t="s">
-        <v>346</v>
+        <v>328</v>
       </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A107" s="6" t="s">
-        <v>383</v>
-      </c>
-      <c r="B107" s="13" t="s">
-        <v>384</v>
-      </c>
-      <c r="C107" s="14" t="s">
-        <v>385</v>
+        <v>365</v>
+      </c>
+      <c r="B107" s="11" t="s">
+        <v>363</v>
+      </c>
+      <c r="C107" s="12" t="s">
+        <v>364</v>
       </c>
       <c r="D107" s="6" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="E107" s="6">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F107" s="6" t="s">
-        <v>373</v>
+        <v>355</v>
       </c>
       <c r="G107" s="9" t="s">
         <v>42</v>
@@ -5507,27 +5540,27 @@
         <v>67</v>
       </c>
       <c r="I107" s="6" t="s">
-        <v>346</v>
+        <v>328</v>
       </c>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A108" s="6" t="s">
-        <v>386</v>
-      </c>
-      <c r="B108" s="13" t="s">
-        <v>387</v>
-      </c>
-      <c r="C108" s="14" t="s">
-        <v>388</v>
+        <v>368</v>
+      </c>
+      <c r="B108" s="11" t="s">
+        <v>366</v>
+      </c>
+      <c r="C108" s="12" t="s">
+        <v>367</v>
       </c>
       <c r="D108" s="6" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E108" s="6">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F108" s="6" t="s">
-        <v>373</v>
+        <v>355</v>
       </c>
       <c r="G108" s="9" t="s">
         <v>42</v>
@@ -5536,27 +5569,27 @@
         <v>67</v>
       </c>
       <c r="I108" s="6" t="s">
-        <v>346</v>
+        <v>328</v>
       </c>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A109" s="6" t="s">
-        <v>389</v>
-      </c>
-      <c r="B109" s="13" t="s">
-        <v>390</v>
-      </c>
-      <c r="C109" s="14" t="s">
-        <v>391</v>
+        <v>371</v>
+      </c>
+      <c r="B109" s="11" t="s">
+        <v>369</v>
+      </c>
+      <c r="C109" s="12" t="s">
+        <v>370</v>
       </c>
       <c r="D109" s="6" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E109" s="6">
         <v>10</v>
       </c>
       <c r="F109" s="6" t="s">
-        <v>373</v>
+        <v>355</v>
       </c>
       <c r="G109" s="9" t="s">
         <v>42</v>
@@ -5565,85 +5598,85 @@
         <v>67</v>
       </c>
       <c r="I109" s="6" t="s">
-        <v>346</v>
+        <v>328</v>
       </c>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A110" s="6" t="s">
-        <v>392</v>
-      </c>
-      <c r="B110" s="13" t="s">
-        <v>393</v>
-      </c>
-      <c r="C110" s="14" t="s">
-        <v>394</v>
+        <v>374</v>
+      </c>
+      <c r="B110" s="11" t="s">
+        <v>372</v>
+      </c>
+      <c r="C110" s="12" t="s">
+        <v>373</v>
       </c>
       <c r="D110" s="6" t="s">
-        <v>11</v>
+        <v>63</v>
       </c>
       <c r="E110" s="6">
         <v>10</v>
       </c>
       <c r="F110" s="6" t="s">
-        <v>395</v>
+        <v>355</v>
       </c>
       <c r="G110" s="9" t="s">
-        <v>96</v>
+        <v>42</v>
       </c>
       <c r="H110" s="6" t="s">
         <v>67</v>
       </c>
       <c r="I110" s="6" t="s">
-        <v>346</v>
+        <v>328</v>
       </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A111" s="6" t="s">
-        <v>396</v>
-      </c>
-      <c r="B111" s="13" t="s">
-        <v>397</v>
-      </c>
-      <c r="C111" s="14" t="s">
-        <v>344</v>
+        <v>378</v>
+      </c>
+      <c r="B111" s="11" t="s">
+        <v>375</v>
+      </c>
+      <c r="C111" s="12" t="s">
+        <v>376</v>
       </c>
       <c r="D111" s="6" t="s">
         <v>11</v>
       </c>
       <c r="E111" s="6">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F111" s="6" t="s">
-        <v>398</v>
+        <v>377</v>
       </c>
       <c r="G111" s="9" t="s">
-        <v>13</v>
+        <v>96</v>
       </c>
       <c r="H111" s="6" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="I111" s="6" t="s">
-        <v>399</v>
+        <v>328</v>
       </c>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A112" s="6" t="s">
-        <v>400</v>
-      </c>
-      <c r="B112" s="13" t="s">
-        <v>401</v>
-      </c>
-      <c r="C112" s="14" t="s">
-        <v>349</v>
+        <v>382</v>
+      </c>
+      <c r="B112" s="11" t="s">
+        <v>379</v>
+      </c>
+      <c r="C112" s="12" t="s">
+        <v>326</v>
       </c>
       <c r="D112" s="6" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E112" s="6">
         <v>2</v>
       </c>
       <c r="F112" s="6" t="s">
-        <v>398</v>
+        <v>380</v>
       </c>
       <c r="G112" s="9" t="s">
         <v>13</v>
@@ -5652,27 +5685,27 @@
         <v>71</v>
       </c>
       <c r="I112" s="6" t="s">
-        <v>399</v>
+        <v>381</v>
       </c>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A113" s="6" t="s">
-        <v>402</v>
-      </c>
-      <c r="B113" s="13" t="s">
-        <v>403</v>
-      </c>
-      <c r="C113" s="14" t="s">
-        <v>404</v>
+        <v>384</v>
+      </c>
+      <c r="B113" s="11" t="s">
+        <v>383</v>
+      </c>
+      <c r="C113" s="12" t="s">
+        <v>331</v>
       </c>
       <c r="D113" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E113" s="6">
         <v>2</v>
       </c>
       <c r="F113" s="6" t="s">
-        <v>398</v>
+        <v>380</v>
       </c>
       <c r="G113" s="9" t="s">
         <v>13</v>
@@ -5681,114 +5714,114 @@
         <v>71</v>
       </c>
       <c r="I113" s="6" t="s">
-        <v>399</v>
+        <v>381</v>
       </c>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A114" s="6" t="s">
-        <v>405</v>
-      </c>
-      <c r="B114" s="13" t="s">
-        <v>406</v>
-      </c>
-      <c r="C114" s="14" t="s">
-        <v>355</v>
+        <v>387</v>
+      </c>
+      <c r="B114" s="11" t="s">
+        <v>385</v>
+      </c>
+      <c r="C114" s="12" t="s">
+        <v>386</v>
       </c>
       <c r="D114" s="6" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="E114" s="6">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F114" s="6" t="s">
-        <v>407</v>
+        <v>380</v>
       </c>
       <c r="G114" s="9" t="s">
-        <v>235</v>
+        <v>13</v>
       </c>
       <c r="H114" s="6" t="s">
         <v>71</v>
       </c>
       <c r="I114" s="6" t="s">
-        <v>399</v>
+        <v>381</v>
       </c>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A115" s="6" t="s">
-        <v>408</v>
-      </c>
-      <c r="B115" s="13" t="s">
-        <v>409</v>
-      </c>
-      <c r="C115" s="14" t="s">
-        <v>359</v>
+        <v>390</v>
+      </c>
+      <c r="B115" s="11" t="s">
+        <v>388</v>
+      </c>
+      <c r="C115" s="12" t="s">
+        <v>337</v>
       </c>
       <c r="D115" s="6" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E115" s="6">
         <v>8</v>
       </c>
       <c r="F115" s="6" t="s">
-        <v>407</v>
+        <v>389</v>
       </c>
       <c r="G115" s="9" t="s">
-        <v>235</v>
+        <v>222</v>
       </c>
       <c r="H115" s="6" t="s">
         <v>71</v>
       </c>
       <c r="I115" s="6" t="s">
-        <v>399</v>
+        <v>381</v>
       </c>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A116" s="6" t="s">
-        <v>410</v>
-      </c>
-      <c r="B116" s="13" t="s">
-        <v>411</v>
-      </c>
-      <c r="C116" s="14" t="s">
-        <v>362</v>
+        <v>392</v>
+      </c>
+      <c r="B116" s="11" t="s">
+        <v>391</v>
+      </c>
+      <c r="C116" s="12" t="s">
+        <v>341</v>
       </c>
       <c r="D116" s="6" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E116" s="6">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F116" s="6" t="s">
-        <v>412</v>
+        <v>389</v>
       </c>
       <c r="G116" s="9" t="s">
-        <v>27</v>
+        <v>222</v>
       </c>
       <c r="H116" s="6" t="s">
         <v>71</v>
       </c>
       <c r="I116" s="6" t="s">
-        <v>399</v>
+        <v>381</v>
       </c>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A117" s="6" t="s">
-        <v>413</v>
-      </c>
-      <c r="B117" s="13" t="s">
-        <v>414</v>
-      </c>
-      <c r="C117" s="14" t="s">
-        <v>366</v>
+        <v>395</v>
+      </c>
+      <c r="B117" s="11" t="s">
+        <v>393</v>
+      </c>
+      <c r="C117" s="12" t="s">
+        <v>344</v>
       </c>
       <c r="D117" s="6" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E117" s="6">
         <v>4</v>
       </c>
       <c r="F117" s="6" t="s">
-        <v>412</v>
+        <v>394</v>
       </c>
       <c r="G117" s="9" t="s">
         <v>27</v>
@@ -5797,27 +5830,27 @@
         <v>71</v>
       </c>
       <c r="I117" s="6" t="s">
-        <v>399</v>
+        <v>381</v>
       </c>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A118" s="6" t="s">
-        <v>415</v>
-      </c>
-      <c r="B118" s="13" t="s">
-        <v>416</v>
-      </c>
-      <c r="C118" s="14" t="s">
-        <v>369</v>
+        <v>397</v>
+      </c>
+      <c r="B118" s="11" t="s">
+        <v>396</v>
+      </c>
+      <c r="C118" s="12" t="s">
+        <v>348</v>
       </c>
       <c r="D118" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E118" s="6">
         <v>4</v>
       </c>
       <c r="F118" s="6" t="s">
-        <v>412</v>
+        <v>394</v>
       </c>
       <c r="G118" s="9" t="s">
         <v>27</v>
@@ -5826,56 +5859,56 @@
         <v>71</v>
       </c>
       <c r="I118" s="6" t="s">
-        <v>399</v>
+        <v>381</v>
       </c>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A119" s="6" t="s">
-        <v>417</v>
-      </c>
-      <c r="B119" s="13" t="s">
-        <v>418</v>
-      </c>
-      <c r="C119" s="14" t="s">
-        <v>372</v>
+        <v>399</v>
+      </c>
+      <c r="B119" s="11" t="s">
+        <v>398</v>
+      </c>
+      <c r="C119" s="12" t="s">
+        <v>351</v>
       </c>
       <c r="D119" s="6" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="E119" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F119" s="6" t="s">
-        <v>419</v>
+        <v>394</v>
       </c>
       <c r="G119" s="9" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="H119" s="6" t="s">
         <v>71</v>
       </c>
       <c r="I119" s="6" t="s">
-        <v>399</v>
+        <v>381</v>
       </c>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A120" s="6" t="s">
-        <v>420</v>
-      </c>
-      <c r="B120" s="13" t="s">
-        <v>421</v>
-      </c>
-      <c r="C120" s="14" t="s">
-        <v>376</v>
+        <v>402</v>
+      </c>
+      <c r="B120" s="11" t="s">
+        <v>400</v>
+      </c>
+      <c r="C120" s="12" t="s">
+        <v>354</v>
       </c>
       <c r="D120" s="6" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E120" s="6">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F120" s="6" t="s">
-        <v>419</v>
+        <v>401</v>
       </c>
       <c r="G120" s="9" t="s">
         <v>42</v>
@@ -5884,27 +5917,27 @@
         <v>71</v>
       </c>
       <c r="I120" s="6" t="s">
-        <v>399</v>
+        <v>381</v>
       </c>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A121" s="6" t="s">
-        <v>422</v>
-      </c>
-      <c r="B121" s="13" t="s">
-        <v>423</v>
-      </c>
-      <c r="C121" s="14" t="s">
-        <v>379</v>
+        <v>404</v>
+      </c>
+      <c r="B121" s="11" t="s">
+        <v>403</v>
+      </c>
+      <c r="C121" s="12" t="s">
+        <v>358</v>
       </c>
       <c r="D121" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E121" s="6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F121" s="6" t="s">
-        <v>419</v>
+        <v>401</v>
       </c>
       <c r="G121" s="9" t="s">
         <v>42</v>
@@ -5913,27 +5946,27 @@
         <v>71</v>
       </c>
       <c r="I121" s="6" t="s">
-        <v>399</v>
+        <v>381</v>
       </c>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A122" s="6" t="s">
-        <v>424</v>
-      </c>
-      <c r="B122" s="13" t="s">
-        <v>425</v>
-      </c>
-      <c r="C122" s="14" t="s">
-        <v>382</v>
+        <v>406</v>
+      </c>
+      <c r="B122" s="11" t="s">
+        <v>405</v>
+      </c>
+      <c r="C122" s="12" t="s">
+        <v>361</v>
       </c>
       <c r="D122" s="6" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="E122" s="6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F122" s="6" t="s">
-        <v>419</v>
+        <v>401</v>
       </c>
       <c r="G122" s="9" t="s">
         <v>42</v>
@@ -5942,27 +5975,27 @@
         <v>71</v>
       </c>
       <c r="I122" s="6" t="s">
-        <v>399</v>
+        <v>381</v>
       </c>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A123" s="6" t="s">
-        <v>426</v>
-      </c>
-      <c r="B123" s="13" t="s">
-        <v>427</v>
-      </c>
-      <c r="C123" s="14" t="s">
-        <v>385</v>
+        <v>408</v>
+      </c>
+      <c r="B123" s="11" t="s">
+        <v>407</v>
+      </c>
+      <c r="C123" s="12" t="s">
+        <v>364</v>
       </c>
       <c r="D123" s="6" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="E123" s="6">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F123" s="6" t="s">
-        <v>419</v>
+        <v>401</v>
       </c>
       <c r="G123" s="9" t="s">
         <v>42</v>
@@ -5971,27 +6004,27 @@
         <v>71</v>
       </c>
       <c r="I123" s="6" t="s">
-        <v>399</v>
+        <v>381</v>
       </c>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A124" s="6" t="s">
-        <v>428</v>
-      </c>
-      <c r="B124" s="13" t="s">
-        <v>429</v>
-      </c>
-      <c r="C124" s="14" t="s">
-        <v>388</v>
+        <v>410</v>
+      </c>
+      <c r="B124" s="11" t="s">
+        <v>409</v>
+      </c>
+      <c r="C124" s="12" t="s">
+        <v>367</v>
       </c>
       <c r="D124" s="6" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E124" s="6">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F124" s="6" t="s">
-        <v>419</v>
+        <v>401</v>
       </c>
       <c r="G124" s="9" t="s">
         <v>42</v>
@@ -6000,27 +6033,27 @@
         <v>71</v>
       </c>
       <c r="I124" s="6" t="s">
-        <v>399</v>
+        <v>381</v>
       </c>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A125" s="6" t="s">
-        <v>430</v>
-      </c>
-      <c r="B125" s="13" t="s">
-        <v>431</v>
-      </c>
-      <c r="C125" s="14" t="s">
-        <v>391</v>
+        <v>412</v>
+      </c>
+      <c r="B125" s="11" t="s">
+        <v>411</v>
+      </c>
+      <c r="C125" s="12" t="s">
+        <v>370</v>
       </c>
       <c r="D125" s="6" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E125" s="6">
         <v>10</v>
       </c>
       <c r="F125" s="6" t="s">
-        <v>419</v>
+        <v>401</v>
       </c>
       <c r="G125" s="9" t="s">
         <v>42</v>
@@ -6029,85 +6062,85 @@
         <v>71</v>
       </c>
       <c r="I125" s="6" t="s">
-        <v>399</v>
+        <v>381</v>
       </c>
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A126" s="6" t="s">
-        <v>432</v>
-      </c>
-      <c r="B126" s="13" t="s">
-        <v>433</v>
-      </c>
-      <c r="C126" s="14" t="s">
-        <v>394</v>
+        <v>414</v>
+      </c>
+      <c r="B126" s="11" t="s">
+        <v>413</v>
+      </c>
+      <c r="C126" s="12" t="s">
+        <v>373</v>
       </c>
       <c r="D126" s="6" t="s">
-        <v>11</v>
+        <v>63</v>
       </c>
       <c r="E126" s="6">
         <v>10</v>
       </c>
       <c r="F126" s="6" t="s">
-        <v>434</v>
+        <v>401</v>
       </c>
       <c r="G126" s="9" t="s">
-        <v>96</v>
+        <v>42</v>
       </c>
       <c r="H126" s="6" t="s">
         <v>71</v>
       </c>
       <c r="I126" s="6" t="s">
-        <v>399</v>
+        <v>381</v>
       </c>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A127" s="6" t="s">
-        <v>435</v>
-      </c>
-      <c r="B127" s="13" t="s">
-        <v>436</v>
-      </c>
-      <c r="C127" s="14" t="s">
-        <v>344</v>
+        <v>417</v>
+      </c>
+      <c r="B127" s="11" t="s">
+        <v>415</v>
+      </c>
+      <c r="C127" s="12" t="s">
+        <v>376</v>
       </c>
       <c r="D127" s="6" t="s">
         <v>11</v>
       </c>
       <c r="E127" s="6">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F127" s="6" t="s">
-        <v>437</v>
+        <v>416</v>
       </c>
       <c r="G127" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="H127" s="6">
-        <v>10</v>
+        <v>96</v>
+      </c>
+      <c r="H127" s="6" t="s">
+        <v>71</v>
       </c>
       <c r="I127" s="6" t="s">
-        <v>438</v>
+        <v>381</v>
       </c>
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A128" s="6" t="s">
-        <v>439</v>
-      </c>
-      <c r="B128" s="13" t="s">
-        <v>440</v>
-      </c>
-      <c r="C128" s="14" t="s">
-        <v>349</v>
+        <v>421</v>
+      </c>
+      <c r="B128" s="11" t="s">
+        <v>418</v>
+      </c>
+      <c r="C128" s="12" t="s">
+        <v>326</v>
       </c>
       <c r="D128" s="6" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E128" s="6">
         <v>2</v>
       </c>
       <c r="F128" s="6" t="s">
-        <v>437</v>
+        <v>419</v>
       </c>
       <c r="G128" s="9" t="s">
         <v>13</v>
@@ -6116,27 +6149,27 @@
         <v>10</v>
       </c>
       <c r="I128" s="6" t="s">
-        <v>438</v>
+        <v>420</v>
       </c>
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A129" s="6" t="s">
-        <v>441</v>
-      </c>
-      <c r="B129" s="13" t="s">
-        <v>442</v>
-      </c>
-      <c r="C129" s="14" t="s">
-        <v>404</v>
+        <v>423</v>
+      </c>
+      <c r="B129" s="11" t="s">
+        <v>422</v>
+      </c>
+      <c r="C129" s="12" t="s">
+        <v>331</v>
       </c>
       <c r="D129" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E129" s="6">
         <v>2</v>
       </c>
       <c r="F129" s="6" t="s">
-        <v>437</v>
+        <v>419</v>
       </c>
       <c r="G129" s="9" t="s">
         <v>13</v>
@@ -6145,114 +6178,114 @@
         <v>10</v>
       </c>
       <c r="I129" s="6" t="s">
-        <v>438</v>
+        <v>420</v>
       </c>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A130" s="6" t="s">
-        <v>443</v>
-      </c>
-      <c r="B130" s="13" t="s">
-        <v>444</v>
-      </c>
-      <c r="C130" s="14" t="s">
-        <v>355</v>
+        <v>425</v>
+      </c>
+      <c r="B130" s="11" t="s">
+        <v>424</v>
+      </c>
+      <c r="C130" s="12" t="s">
+        <v>386</v>
       </c>
       <c r="D130" s="6" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="E130" s="6">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F130" s="6" t="s">
-        <v>445</v>
+        <v>419</v>
       </c>
       <c r="G130" s="9" t="s">
-        <v>235</v>
+        <v>13</v>
       </c>
       <c r="H130" s="6">
         <v>10</v>
       </c>
       <c r="I130" s="6" t="s">
-        <v>438</v>
+        <v>420</v>
       </c>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A131" s="6" t="s">
-        <v>446</v>
-      </c>
-      <c r="B131" s="13" t="s">
-        <v>447</v>
-      </c>
-      <c r="C131" s="14" t="s">
-        <v>359</v>
+        <v>428</v>
+      </c>
+      <c r="B131" s="11" t="s">
+        <v>426</v>
+      </c>
+      <c r="C131" s="12" t="s">
+        <v>337</v>
       </c>
       <c r="D131" s="6" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E131" s="6">
         <v>8</v>
       </c>
       <c r="F131" s="6" t="s">
-        <v>445</v>
+        <v>427</v>
       </c>
       <c r="G131" s="9" t="s">
-        <v>235</v>
+        <v>222</v>
       </c>
       <c r="H131" s="6">
         <v>10</v>
       </c>
       <c r="I131" s="6" t="s">
-        <v>438</v>
+        <v>420</v>
       </c>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A132" s="6" t="s">
-        <v>448</v>
-      </c>
-      <c r="B132" s="13" t="s">
-        <v>449</v>
-      </c>
-      <c r="C132" s="14" t="s">
-        <v>362</v>
+        <v>430</v>
+      </c>
+      <c r="B132" s="11" t="s">
+        <v>429</v>
+      </c>
+      <c r="C132" s="12" t="s">
+        <v>341</v>
       </c>
       <c r="D132" s="6" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E132" s="6">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F132" s="6" t="s">
-        <v>450</v>
+        <v>427</v>
       </c>
       <c r="G132" s="9" t="s">
-        <v>27</v>
+        <v>222</v>
       </c>
       <c r="H132" s="6">
         <v>10</v>
       </c>
       <c r="I132" s="6" t="s">
-        <v>438</v>
+        <v>420</v>
       </c>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A133" s="6" t="s">
-        <v>451</v>
-      </c>
-      <c r="B133" s="13" t="s">
-        <v>452</v>
-      </c>
-      <c r="C133" s="14" t="s">
-        <v>366</v>
+        <v>433</v>
+      </c>
+      <c r="B133" s="11" t="s">
+        <v>431</v>
+      </c>
+      <c r="C133" s="12" t="s">
+        <v>344</v>
       </c>
       <c r="D133" s="6" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E133" s="6">
         <v>4</v>
       </c>
       <c r="F133" s="6" t="s">
-        <v>450</v>
+        <v>432</v>
       </c>
       <c r="G133" s="9" t="s">
         <v>27</v>
@@ -6261,27 +6294,27 @@
         <v>10</v>
       </c>
       <c r="I133" s="6" t="s">
-        <v>438</v>
+        <v>420</v>
       </c>
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A134" s="6" t="s">
-        <v>453</v>
-      </c>
-      <c r="B134" s="13" t="s">
-        <v>454</v>
-      </c>
-      <c r="C134" s="14" t="s">
-        <v>369</v>
+        <v>435</v>
+      </c>
+      <c r="B134" s="11" t="s">
+        <v>434</v>
+      </c>
+      <c r="C134" s="12" t="s">
+        <v>348</v>
       </c>
       <c r="D134" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E134" s="6">
         <v>4</v>
       </c>
       <c r="F134" s="6" t="s">
-        <v>450</v>
+        <v>432</v>
       </c>
       <c r="G134" s="9" t="s">
         <v>27</v>
@@ -6290,56 +6323,56 @@
         <v>10</v>
       </c>
       <c r="I134" s="6" t="s">
-        <v>438</v>
+        <v>420</v>
       </c>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A135" s="6" t="s">
-        <v>455</v>
-      </c>
-      <c r="B135" s="13" t="s">
-        <v>456</v>
-      </c>
-      <c r="C135" s="14" t="s">
-        <v>372</v>
+        <v>437</v>
+      </c>
+      <c r="B135" s="11" t="s">
+        <v>436</v>
+      </c>
+      <c r="C135" s="12" t="s">
+        <v>351</v>
       </c>
       <c r="D135" s="6" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="E135" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F135" s="6" t="s">
-        <v>457</v>
+        <v>432</v>
       </c>
       <c r="G135" s="9" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="H135" s="6">
         <v>10</v>
       </c>
       <c r="I135" s="6" t="s">
-        <v>438</v>
+        <v>420</v>
       </c>
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A136" s="6" t="s">
-        <v>458</v>
-      </c>
-      <c r="B136" s="13" t="s">
-        <v>459</v>
-      </c>
-      <c r="C136" s="14" t="s">
-        <v>376</v>
+        <v>440</v>
+      </c>
+      <c r="B136" s="11" t="s">
+        <v>438</v>
+      </c>
+      <c r="C136" s="12" t="s">
+        <v>354</v>
       </c>
       <c r="D136" s="6" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E136" s="6">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F136" s="6" t="s">
-        <v>457</v>
+        <v>439</v>
       </c>
       <c r="G136" s="9" t="s">
         <v>42</v>
@@ -6348,27 +6381,27 @@
         <v>10</v>
       </c>
       <c r="I136" s="6" t="s">
-        <v>438</v>
+        <v>420</v>
       </c>
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A137" s="6" t="s">
-        <v>460</v>
-      </c>
-      <c r="B137" s="13" t="s">
-        <v>461</v>
-      </c>
-      <c r="C137" s="14" t="s">
-        <v>379</v>
+        <v>442</v>
+      </c>
+      <c r="B137" s="11" t="s">
+        <v>441</v>
+      </c>
+      <c r="C137" s="12" t="s">
+        <v>358</v>
       </c>
       <c r="D137" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E137" s="6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F137" s="6" t="s">
-        <v>457</v>
+        <v>439</v>
       </c>
       <c r="G137" s="9" t="s">
         <v>42</v>
@@ -6377,27 +6410,27 @@
         <v>10</v>
       </c>
       <c r="I137" s="6" t="s">
-        <v>438</v>
+        <v>420</v>
       </c>
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A138" s="6" t="s">
-        <v>462</v>
-      </c>
-      <c r="B138" s="13" t="s">
-        <v>463</v>
-      </c>
-      <c r="C138" s="14" t="s">
-        <v>382</v>
+        <v>444</v>
+      </c>
+      <c r="B138" s="11" t="s">
+        <v>443</v>
+      </c>
+      <c r="C138" s="12" t="s">
+        <v>361</v>
       </c>
       <c r="D138" s="6" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="E138" s="6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F138" s="6" t="s">
-        <v>457</v>
+        <v>439</v>
       </c>
       <c r="G138" s="9" t="s">
         <v>42</v>
@@ -6406,27 +6439,27 @@
         <v>10</v>
       </c>
       <c r="I138" s="6" t="s">
-        <v>438</v>
+        <v>420</v>
       </c>
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A139" s="6" t="s">
-        <v>464</v>
-      </c>
-      <c r="B139" s="13" t="s">
-        <v>465</v>
-      </c>
-      <c r="C139" s="14" t="s">
-        <v>385</v>
+        <v>446</v>
+      </c>
+      <c r="B139" s="11" t="s">
+        <v>445</v>
+      </c>
+      <c r="C139" s="12" t="s">
+        <v>364</v>
       </c>
       <c r="D139" s="6" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="E139" s="6">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F139" s="6" t="s">
-        <v>457</v>
+        <v>439</v>
       </c>
       <c r="G139" s="9" t="s">
         <v>42</v>
@@ -6435,27 +6468,27 @@
         <v>10</v>
       </c>
       <c r="I139" s="6" t="s">
-        <v>438</v>
+        <v>420</v>
       </c>
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A140" s="6" t="s">
-        <v>466</v>
-      </c>
-      <c r="B140" s="13" t="s">
-        <v>467</v>
-      </c>
-      <c r="C140" s="14" t="s">
-        <v>388</v>
+        <v>448</v>
+      </c>
+      <c r="B140" s="11" t="s">
+        <v>447</v>
+      </c>
+      <c r="C140" s="12" t="s">
+        <v>367</v>
       </c>
       <c r="D140" s="6" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E140" s="6">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F140" s="6" t="s">
-        <v>457</v>
+        <v>439</v>
       </c>
       <c r="G140" s="9" t="s">
         <v>42</v>
@@ -6464,27 +6497,27 @@
         <v>10</v>
       </c>
       <c r="I140" s="6" t="s">
-        <v>438</v>
+        <v>420</v>
       </c>
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A141" s="6" t="s">
-        <v>468</v>
-      </c>
-      <c r="B141" s="13" t="s">
-        <v>469</v>
-      </c>
-      <c r="C141" s="14" t="s">
-        <v>391</v>
+        <v>450</v>
+      </c>
+      <c r="B141" s="11" t="s">
+        <v>449</v>
+      </c>
+      <c r="C141" s="12" t="s">
+        <v>370</v>
       </c>
       <c r="D141" s="6" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E141" s="6">
         <v>10</v>
       </c>
       <c r="F141" s="6" t="s">
-        <v>457</v>
+        <v>439</v>
       </c>
       <c r="G141" s="9" t="s">
         <v>42</v>
@@ -6493,85 +6526,85 @@
         <v>10</v>
       </c>
       <c r="I141" s="6" t="s">
-        <v>438</v>
+        <v>420</v>
       </c>
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A142" s="6" t="s">
-        <v>470</v>
-      </c>
-      <c r="B142" s="13" t="s">
-        <v>471</v>
-      </c>
-      <c r="C142" s="14" t="s">
-        <v>394</v>
+        <v>452</v>
+      </c>
+      <c r="B142" s="11" t="s">
+        <v>451</v>
+      </c>
+      <c r="C142" s="12" t="s">
+        <v>373</v>
       </c>
       <c r="D142" s="6" t="s">
-        <v>11</v>
+        <v>63</v>
       </c>
       <c r="E142" s="6">
         <v>10</v>
       </c>
       <c r="F142" s="6" t="s">
-        <v>472</v>
+        <v>439</v>
       </c>
       <c r="G142" s="9" t="s">
-        <v>96</v>
+        <v>42</v>
       </c>
       <c r="H142" s="6">
         <v>10</v>
       </c>
       <c r="I142" s="6" t="s">
-        <v>438</v>
+        <v>420</v>
       </c>
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A143" s="6" t="s">
-        <v>473</v>
-      </c>
-      <c r="B143" s="13" t="s">
-        <v>474</v>
-      </c>
-      <c r="C143" s="14" t="s">
-        <v>344</v>
+        <v>455</v>
+      </c>
+      <c r="B143" s="11" t="s">
+        <v>453</v>
+      </c>
+      <c r="C143" s="12" t="s">
+        <v>376</v>
       </c>
       <c r="D143" s="6" t="s">
         <v>11</v>
       </c>
       <c r="E143" s="6">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F143" s="6" t="s">
-        <v>475</v>
+        <v>454</v>
       </c>
       <c r="G143" s="9" t="s">
-        <v>13</v>
+        <v>96</v>
       </c>
       <c r="H143" s="6">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I143" s="6" t="s">
-        <v>476</v>
+        <v>420</v>
       </c>
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A144" s="6" t="s">
-        <v>477</v>
-      </c>
-      <c r="B144" s="13" t="s">
-        <v>478</v>
-      </c>
-      <c r="C144" s="14" t="s">
-        <v>349</v>
+        <v>459</v>
+      </c>
+      <c r="B144" s="11" t="s">
+        <v>456</v>
+      </c>
+      <c r="C144" s="12" t="s">
+        <v>326</v>
       </c>
       <c r="D144" s="6" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E144" s="6">
         <v>2</v>
       </c>
       <c r="F144" s="6" t="s">
-        <v>475</v>
+        <v>457</v>
       </c>
       <c r="G144" s="9" t="s">
         <v>13</v>
@@ -6580,27 +6613,27 @@
         <v>11</v>
       </c>
       <c r="I144" s="6" t="s">
-        <v>476</v>
+        <v>458</v>
       </c>
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A145" s="6" t="s">
-        <v>479</v>
-      </c>
-      <c r="B145" s="13" t="s">
-        <v>480</v>
-      </c>
-      <c r="C145" s="14" t="s">
-        <v>404</v>
+        <v>461</v>
+      </c>
+      <c r="B145" s="11" t="s">
+        <v>460</v>
+      </c>
+      <c r="C145" s="12" t="s">
+        <v>331</v>
       </c>
       <c r="D145" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E145" s="6">
         <v>2</v>
       </c>
       <c r="F145" s="6" t="s">
-        <v>475</v>
+        <v>457</v>
       </c>
       <c r="G145" s="9" t="s">
         <v>13</v>
@@ -6609,114 +6642,114 @@
         <v>11</v>
       </c>
       <c r="I145" s="6" t="s">
-        <v>476</v>
+        <v>458</v>
       </c>
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A146" s="6" t="s">
-        <v>481</v>
-      </c>
-      <c r="B146" s="13" t="s">
-        <v>482</v>
-      </c>
-      <c r="C146" s="14" t="s">
-        <v>355</v>
+        <v>463</v>
+      </c>
+      <c r="B146" s="11" t="s">
+        <v>462</v>
+      </c>
+      <c r="C146" s="12" t="s">
+        <v>386</v>
       </c>
       <c r="D146" s="6" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="E146" s="6">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F146" s="6" t="s">
-        <v>483</v>
+        <v>457</v>
       </c>
       <c r="G146" s="9" t="s">
-        <v>235</v>
+        <v>13</v>
       </c>
       <c r="H146" s="6">
         <v>11</v>
       </c>
       <c r="I146" s="6" t="s">
-        <v>476</v>
+        <v>458</v>
       </c>
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A147" s="6" t="s">
-        <v>484</v>
-      </c>
-      <c r="B147" s="13" t="s">
-        <v>485</v>
-      </c>
-      <c r="C147" s="14" t="s">
-        <v>359</v>
+        <v>466</v>
+      </c>
+      <c r="B147" s="11" t="s">
+        <v>464</v>
+      </c>
+      <c r="C147" s="12" t="s">
+        <v>337</v>
       </c>
       <c r="D147" s="6" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E147" s="6">
         <v>8</v>
       </c>
       <c r="F147" s="6" t="s">
-        <v>483</v>
+        <v>465</v>
       </c>
       <c r="G147" s="9" t="s">
-        <v>235</v>
+        <v>222</v>
       </c>
       <c r="H147" s="6">
         <v>11</v>
       </c>
       <c r="I147" s="6" t="s">
-        <v>476</v>
+        <v>458</v>
       </c>
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A148" s="6" t="s">
-        <v>486</v>
-      </c>
-      <c r="B148" s="13" t="s">
-        <v>487</v>
-      </c>
-      <c r="C148" s="14" t="s">
-        <v>362</v>
+        <v>468</v>
+      </c>
+      <c r="B148" s="11" t="s">
+        <v>467</v>
+      </c>
+      <c r="C148" s="12" t="s">
+        <v>341</v>
       </c>
       <c r="D148" s="6" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E148" s="6">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F148" s="6" t="s">
-        <v>488</v>
+        <v>465</v>
       </c>
       <c r="G148" s="9" t="s">
-        <v>27</v>
+        <v>222</v>
       </c>
       <c r="H148" s="6">
         <v>11</v>
       </c>
       <c r="I148" s="6" t="s">
-        <v>476</v>
+        <v>458</v>
       </c>
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A149" s="6" t="s">
-        <v>489</v>
-      </c>
-      <c r="B149" s="13" t="s">
-        <v>490</v>
-      </c>
-      <c r="C149" s="14" t="s">
-        <v>366</v>
+        <v>471</v>
+      </c>
+      <c r="B149" s="11" t="s">
+        <v>469</v>
+      </c>
+      <c r="C149" s="12" t="s">
+        <v>344</v>
       </c>
       <c r="D149" s="6" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E149" s="6">
         <v>4</v>
       </c>
       <c r="F149" s="6" t="s">
-        <v>488</v>
+        <v>470</v>
       </c>
       <c r="G149" s="9" t="s">
         <v>27</v>
@@ -6725,27 +6758,27 @@
         <v>11</v>
       </c>
       <c r="I149" s="6" t="s">
-        <v>476</v>
+        <v>458</v>
       </c>
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A150" s="6" t="s">
-        <v>491</v>
-      </c>
-      <c r="B150" s="13" t="s">
-        <v>492</v>
-      </c>
-      <c r="C150" s="14" t="s">
-        <v>369</v>
+        <v>473</v>
+      </c>
+      <c r="B150" s="11" t="s">
+        <v>472</v>
+      </c>
+      <c r="C150" s="12" t="s">
+        <v>348</v>
       </c>
       <c r="D150" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E150" s="6">
         <v>4</v>
       </c>
       <c r="F150" s="6" t="s">
-        <v>488</v>
+        <v>470</v>
       </c>
       <c r="G150" s="9" t="s">
         <v>27</v>
@@ -6754,56 +6787,56 @@
         <v>11</v>
       </c>
       <c r="I150" s="6" t="s">
-        <v>476</v>
+        <v>458</v>
       </c>
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A151" s="6" t="s">
-        <v>493</v>
-      </c>
-      <c r="B151" s="13" t="s">
-        <v>494</v>
-      </c>
-      <c r="C151" s="14" t="s">
-        <v>372</v>
+        <v>475</v>
+      </c>
+      <c r="B151" s="11" t="s">
+        <v>474</v>
+      </c>
+      <c r="C151" s="12" t="s">
+        <v>351</v>
       </c>
       <c r="D151" s="6" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="E151" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F151" s="6" t="s">
-        <v>495</v>
+        <v>470</v>
       </c>
       <c r="G151" s="9" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="H151" s="6">
         <v>11</v>
       </c>
       <c r="I151" s="6" t="s">
-        <v>476</v>
+        <v>458</v>
       </c>
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A152" s="6" t="s">
-        <v>496</v>
-      </c>
-      <c r="B152" s="13" t="s">
-        <v>497</v>
-      </c>
-      <c r="C152" s="14" t="s">
-        <v>376</v>
+        <v>478</v>
+      </c>
+      <c r="B152" s="11" t="s">
+        <v>476</v>
+      </c>
+      <c r="C152" s="12" t="s">
+        <v>354</v>
       </c>
       <c r="D152" s="6" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E152" s="6">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F152" s="6" t="s">
-        <v>495</v>
+        <v>477</v>
       </c>
       <c r="G152" s="9" t="s">
         <v>42</v>
@@ -6812,27 +6845,27 @@
         <v>11</v>
       </c>
       <c r="I152" s="6" t="s">
-        <v>476</v>
+        <v>458</v>
       </c>
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A153" s="6" t="s">
-        <v>498</v>
-      </c>
-      <c r="B153" s="13" t="s">
-        <v>499</v>
-      </c>
-      <c r="C153" s="14" t="s">
-        <v>379</v>
+        <v>480</v>
+      </c>
+      <c r="B153" s="11" t="s">
+        <v>479</v>
+      </c>
+      <c r="C153" s="12" t="s">
+        <v>358</v>
       </c>
       <c r="D153" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E153" s="6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F153" s="6" t="s">
-        <v>495</v>
+        <v>477</v>
       </c>
       <c r="G153" s="9" t="s">
         <v>42</v>
@@ -6841,27 +6874,27 @@
         <v>11</v>
       </c>
       <c r="I153" s="6" t="s">
-        <v>476</v>
+        <v>458</v>
       </c>
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A154" s="6" t="s">
-        <v>500</v>
-      </c>
-      <c r="B154" s="13" t="s">
-        <v>501</v>
-      </c>
-      <c r="C154" s="14" t="s">
-        <v>382</v>
+        <v>482</v>
+      </c>
+      <c r="B154" s="11" t="s">
+        <v>481</v>
+      </c>
+      <c r="C154" s="12" t="s">
+        <v>361</v>
       </c>
       <c r="D154" s="6" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="E154" s="6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F154" s="6" t="s">
-        <v>495</v>
+        <v>477</v>
       </c>
       <c r="G154" s="9" t="s">
         <v>42</v>
@@ -6870,27 +6903,27 @@
         <v>11</v>
       </c>
       <c r="I154" s="6" t="s">
-        <v>476</v>
+        <v>458</v>
       </c>
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A155" s="6" t="s">
-        <v>502</v>
-      </c>
-      <c r="B155" s="13" t="s">
-        <v>503</v>
-      </c>
-      <c r="C155" s="14" t="s">
-        <v>385</v>
+        <v>484</v>
+      </c>
+      <c r="B155" s="11" t="s">
+        <v>483</v>
+      </c>
+      <c r="C155" s="12" t="s">
+        <v>364</v>
       </c>
       <c r="D155" s="6" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="E155" s="6">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F155" s="6" t="s">
-        <v>495</v>
+        <v>477</v>
       </c>
       <c r="G155" s="9" t="s">
         <v>42</v>
@@ -6899,27 +6932,27 @@
         <v>11</v>
       </c>
       <c r="I155" s="6" t="s">
-        <v>476</v>
+        <v>458</v>
       </c>
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A156" s="6" t="s">
-        <v>504</v>
-      </c>
-      <c r="B156" s="13" t="s">
-        <v>505</v>
-      </c>
-      <c r="C156" s="14" t="s">
-        <v>388</v>
+        <v>486</v>
+      </c>
+      <c r="B156" s="11" t="s">
+        <v>485</v>
+      </c>
+      <c r="C156" s="12" t="s">
+        <v>367</v>
       </c>
       <c r="D156" s="6" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E156" s="6">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F156" s="6" t="s">
-        <v>495</v>
+        <v>477</v>
       </c>
       <c r="G156" s="9" t="s">
         <v>42</v>
@@ -6928,85 +6961,85 @@
         <v>11</v>
       </c>
       <c r="I156" s="6" t="s">
-        <v>476</v>
+        <v>458</v>
       </c>
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A157" s="6" t="s">
-        <v>506</v>
-      </c>
-      <c r="B157" s="13" t="s">
-        <v>507</v>
-      </c>
-      <c r="C157" s="14" t="s">
-        <v>391</v>
+        <v>487</v>
+      </c>
+      <c r="B157" s="11" t="s">
+        <v>489</v>
+      </c>
+      <c r="C157" s="12" t="s">
+        <v>376</v>
       </c>
       <c r="D157" s="6" t="s">
-        <v>63</v>
+        <v>11</v>
       </c>
       <c r="E157" s="6">
         <v>10</v>
       </c>
       <c r="F157" s="6" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="G157" s="9" t="s">
-        <v>42</v>
+        <v>96</v>
       </c>
       <c r="H157" s="6">
         <v>11</v>
       </c>
       <c r="I157" s="6" t="s">
-        <v>476</v>
+        <v>458</v>
       </c>
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A158" s="6" t="s">
-        <v>508</v>
-      </c>
-      <c r="B158" s="13" t="s">
-        <v>509</v>
-      </c>
-      <c r="C158" s="14" t="s">
-        <v>394</v>
+        <v>488</v>
+      </c>
+      <c r="B158" s="7" t="s">
+        <v>492</v>
+      </c>
+      <c r="C158" s="8" t="s">
+        <v>493</v>
       </c>
       <c r="D158" s="6" t="s">
         <v>11</v>
       </c>
       <c r="E158" s="6">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F158" s="6" t="s">
-        <v>510</v>
+        <v>494</v>
       </c>
       <c r="G158" s="9" t="s">
-        <v>96</v>
+        <v>13</v>
       </c>
       <c r="H158" s="6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I158" s="6" t="s">
-        <v>476</v>
+        <v>495</v>
       </c>
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A159" s="6" t="s">
-        <v>511</v>
+        <v>491</v>
       </c>
       <c r="B159" s="7" t="s">
-        <v>512</v>
+        <v>497</v>
       </c>
       <c r="C159" s="8" t="s">
-        <v>513</v>
+        <v>498</v>
       </c>
       <c r="D159" s="6" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E159" s="6">
         <v>15</v>
       </c>
       <c r="F159" s="6" t="s">
-        <v>514</v>
+        <v>494</v>
       </c>
       <c r="G159" s="9" t="s">
         <v>13</v>
@@ -7015,27 +7048,27 @@
         <v>12</v>
       </c>
       <c r="I159" s="6" t="s">
-        <v>515</v>
+        <v>495</v>
       </c>
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A160" s="6" t="s">
-        <v>516</v>
+        <v>496</v>
       </c>
       <c r="B160" s="7" t="s">
-        <v>517</v>
+        <v>500</v>
       </c>
       <c r="C160" s="8" t="s">
-        <v>518</v>
+        <v>501</v>
       </c>
       <c r="D160" s="6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E160" s="6">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F160" s="6" t="s">
-        <v>514</v>
+        <v>494</v>
       </c>
       <c r="G160" s="9" t="s">
         <v>13</v>
@@ -7044,56 +7077,56 @@
         <v>12</v>
       </c>
       <c r="I160" s="6" t="s">
-        <v>515</v>
+        <v>495</v>
       </c>
     </row>
     <row r="161" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A161" s="6" t="s">
-        <v>519</v>
+        <v>499</v>
       </c>
       <c r="B161" s="7" t="s">
-        <v>520</v>
+        <v>503</v>
       </c>
       <c r="C161" s="8" t="s">
-        <v>521</v>
+        <v>504</v>
       </c>
       <c r="D161" s="6" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E161" s="6">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F161" s="6" t="s">
-        <v>514</v>
+        <v>505</v>
       </c>
       <c r="G161" s="9" t="s">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="H161" s="6">
         <v>12</v>
       </c>
       <c r="I161" s="6" t="s">
-        <v>515</v>
+        <v>495</v>
       </c>
     </row>
     <row r="162" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A162" s="6" t="s">
-        <v>522</v>
+        <v>502</v>
       </c>
       <c r="B162" s="7" t="s">
-        <v>523</v>
+        <v>507</v>
       </c>
       <c r="C162" s="8" t="s">
-        <v>524</v>
+        <v>508</v>
       </c>
       <c r="D162" s="6" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E162" s="6">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F162" s="6" t="s">
-        <v>525</v>
+        <v>505</v>
       </c>
       <c r="G162" s="9" t="s">
         <v>42</v>
@@ -7102,27 +7135,27 @@
         <v>12</v>
       </c>
       <c r="I162" s="6" t="s">
-        <v>515</v>
+        <v>495</v>
       </c>
     </row>
     <row r="163" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A163" s="6" t="s">
-        <v>526</v>
+        <v>506</v>
       </c>
       <c r="B163" s="7" t="s">
-        <v>527</v>
+        <v>510</v>
       </c>
       <c r="C163" s="8" t="s">
-        <v>528</v>
+        <v>511</v>
       </c>
       <c r="D163" s="6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E163" s="6">
         <v>5</v>
       </c>
       <c r="F163" s="6" t="s">
-        <v>525</v>
+        <v>505</v>
       </c>
       <c r="G163" s="9" t="s">
         <v>42</v>
@@ -7131,27 +7164,27 @@
         <v>12</v>
       </c>
       <c r="I163" s="6" t="s">
-        <v>515</v>
+        <v>495</v>
       </c>
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A164" s="6" t="s">
-        <v>529</v>
+        <v>509</v>
       </c>
       <c r="B164" s="7" t="s">
-        <v>530</v>
+        <v>513</v>
       </c>
       <c r="C164" s="8" t="s">
-        <v>531</v>
+        <v>514</v>
       </c>
       <c r="D164" s="6" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="E164" s="6">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F164" s="6" t="s">
-        <v>525</v>
+        <v>505</v>
       </c>
       <c r="G164" s="9" t="s">
         <v>42</v>
@@ -7160,94 +7193,65 @@
         <v>12</v>
       </c>
       <c r="I164" s="6" t="s">
-        <v>515</v>
+        <v>495</v>
       </c>
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A165" s="6" t="s">
-        <v>532</v>
+        <v>512</v>
       </c>
       <c r="B165" s="7" t="s">
-        <v>533</v>
+        <v>516</v>
       </c>
       <c r="C165" s="8" t="s">
-        <v>534</v>
+        <v>517</v>
       </c>
       <c r="D165" s="6" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="E165" s="6">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F165" s="6" t="s">
-        <v>525</v>
+        <v>518</v>
       </c>
       <c r="G165" s="9" t="s">
-        <v>42</v>
+        <v>519</v>
       </c>
       <c r="H165" s="6">
         <v>12</v>
       </c>
       <c r="I165" s="6" t="s">
-        <v>515</v>
+        <v>495</v>
       </c>
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A166" s="6" t="s">
-        <v>535</v>
+        <v>515</v>
       </c>
       <c r="B166" s="7" t="s">
-        <v>536</v>
+        <v>520</v>
       </c>
       <c r="C166" s="8" t="s">
-        <v>537</v>
+        <v>521</v>
       </c>
       <c r="D166" s="6" t="s">
         <v>11</v>
       </c>
       <c r="E166" s="6">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F166" s="6" t="s">
-        <v>538</v>
+        <v>522</v>
       </c>
       <c r="G166" s="9" t="s">
-        <v>539</v>
+        <v>523</v>
       </c>
       <c r="H166" s="6">
         <v>12</v>
       </c>
       <c r="I166" s="6" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A167" s="6" t="s">
-        <v>540</v>
-      </c>
-      <c r="B167" s="7" t="s">
-        <v>541</v>
-      </c>
-      <c r="C167" s="8" t="s">
-        <v>542</v>
-      </c>
-      <c r="D167" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E167" s="6">
-        <v>10</v>
-      </c>
-      <c r="F167" s="6" t="s">
-        <v>543</v>
-      </c>
-      <c r="G167" s="9" t="s">
-        <v>544</v>
-      </c>
-      <c r="H167" s="6">
-        <v>12</v>
-      </c>
-      <c r="I167" s="6" t="s">
-        <v>515</v>
+        <v>495</v>
       </c>
     </row>
   </sheetData>

--- a/Dim_Componentes_VSP.xlsx
+++ b/Dim_Componentes_VSP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://saludcapitalgovco-my.sharepoint.com/personal/jcleon_saludcapital_gov_co/Documents/Tablas_Referencia_SDS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="24" documentId="13_ncr:1_{F720D04B-7165-412E-9F8E-C8C5050545E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{10EF48B1-1F5D-49B6-A0D4-845644109D3B}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="13_ncr:1_{F720D04B-7165-412E-9F8E-C8C5050545E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BDDAECB0-1F59-40AF-B9CC-1447C6570804}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6625EA50-83D4-486A-A0BA-E91AF6E8BE6B}"/>
   </bookViews>
@@ -2089,6 +2089,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{80F83481-E46E-43DE-9D95-422AF1A554D6}" name="Dim_Componentes_SVSP3" displayName="Dim_Componentes_SVSP3" ref="A1:I166" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9">
   <autoFilter ref="A1:I166" xr:uid="{80F83481-E46E-43DE-9D95-422AF1A554D6}"/>

--- a/Dim_Componentes_VSP.xlsx
+++ b/Dim_Componentes_VSP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://saludcapitalgovco-my.sharepoint.com/personal/jcleon_saludcapital_gov_co/Documents/Tablas_Referencia_SDS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="26" documentId="13_ncr:1_{F720D04B-7165-412E-9F8E-C8C5050545E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BDDAECB0-1F59-40AF-B9CC-1447C6570804}"/>
+  <xr:revisionPtr revIDLastSave="27" documentId="13_ncr:1_{F720D04B-7165-412E-9F8E-C8C5050545E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{87C50F0C-C2A8-4A82-8808-B6D78DDAF585}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6625EA50-83D4-486A-A0BA-E91AF6E8BE6B}"/>
   </bookViews>
@@ -2089,12 +2089,8 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{80F83481-E46E-43DE-9D95-422AF1A554D6}" name="Dim_Componentes_SVSP3" displayName="Dim_Componentes_SVSP3" ref="A1:I166" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{80F83481-E46E-43DE-9D95-422AF1A554D6}" name="Dim_Componentes_SVSP" displayName="Dim_Componentes_SVSP" ref="A1:I166" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9">
   <autoFilter ref="A1:I166" xr:uid="{80F83481-E46E-43DE-9D95-422AF1A554D6}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{B1A27102-7B7B-4FB0-8CDC-B37FBE546E73}" name="Id_Global" dataDxfId="8"/>

--- a/Dim_Componentes_VSP.xlsx
+++ b/Dim_Componentes_VSP.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr codeName="ThisWorkbook"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://saludcapitalgovco-my.sharepoint.com/personal/jcleon_saludcapital_gov_co/Documents/Tablas_Referencia_SDS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="27" documentId="13_ncr:1_{F720D04B-7165-412E-9F8E-C8C5050545E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{87C50F0C-C2A8-4A82-8808-B6D78DDAF585}"/>
+  <xr:revisionPtr revIDLastSave="30" documentId="13_ncr:1_{F720D04B-7165-412E-9F8E-C8C5050545E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1B0C07B3-6302-4408-B8BC-9F5A93E69B56}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6625EA50-83D4-486A-A0BA-E91AF6E8BE6B}"/>
   </bookViews>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1290" uniqueCount="556">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1526" uniqueCount="671">
   <si>
     <t>Id_Global</t>
   </si>
@@ -1719,13 +1719,358 @@
   </si>
   <si>
     <t>Calidad del registro y gestión en fecha de inicio de tratamiento</t>
+  </si>
+  <si>
+    <t>13_1_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> La UPGD cuenta con talento humano Responsable para la Vigilancia en Salud Publica de todos los eventos IAAS incluyendo brotes de IAAS,  capacitado en el proceso de Vigilancia en Salud Publica y Notificación como lo solicita la resolucion 2471 del 2022</t>
+  </si>
+  <si>
+    <t>13_1</t>
+  </si>
+  <si>
+    <t>IAAS - Calidad en la notificación de eventos de interés en salud pública</t>
+  </si>
+  <si>
+    <t>IAAS</t>
+  </si>
+  <si>
+    <t>13_1_2</t>
+  </si>
+  <si>
+    <t>Verificar que la IPS cuente con la implementación, seguimiento y equipo operativo para el Programa de Optimización de antimicrobianos.</t>
+  </si>
+  <si>
+    <t>13_1_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La UPGD cuenta con socializacion en los ultimos 4 meses los protocolos de vigilancia en salud publica de los eventos de notificacion obligatoria de IAAS inlcluyenedo brotes y resistencia antimicrobiana </t>
+  </si>
+  <si>
+    <t>13_1_4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La IPS participa activamente en los comites de IAAS distritales y socializa esta informacion en el comité de infecciones institucional </t>
+  </si>
+  <si>
+    <t>13_1_5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La IPS cuenta con analisis de los indicadores especificos de cada evento según protocolos de IAD, consumo de ATB, IAPMQ de manera mensual y semestra para resistencia antimicrobiana, frente a historicos y cuentan con una meta institucional establecida para cada indicador. </t>
+  </si>
+  <si>
+    <t>13_1_6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La IPS se ha encontrado o se encuentra en riesgo de silencio para IAD, IAPMQ y CAB. </t>
+  </si>
+  <si>
+    <t>13_1_7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La IPS  se ha encontrado o se encuentra en silencio epidemiologico para IAD, IAPMQ, CAB y WHONET </t>
+  </si>
+  <si>
+    <t>13_1_8</t>
+  </si>
+  <si>
+    <t>Revisar la realización de la BAI - IAD ante riesgo de silencio o silencio epidemiologico.</t>
+  </si>
+  <si>
+    <t>13_1_9</t>
+  </si>
+  <si>
+    <t>Cumplimiento de la notificación colectiva IAD, IAPMQ, CAB mensual</t>
+  </si>
+  <si>
+    <t>13_1_10</t>
+  </si>
+  <si>
+    <t>Oportunidad de la notificación colectiva IAD, IAPMQ, CAB mensual</t>
+  </si>
+  <si>
+    <t>13_1_11</t>
+  </si>
+  <si>
+    <t>Oportunidad de la notificación de IAPMQ individual</t>
+  </si>
+  <si>
+    <t>13_2_1</t>
+  </si>
+  <si>
+    <t>Calidad del diligenciamiento del evento IAD colectivo en el aplicativo SIVIGILA</t>
+  </si>
+  <si>
+    <t>13_2</t>
+  </si>
+  <si>
+    <t>IAD - Calidad en la notificación de eventos de interés en salud pública</t>
+  </si>
+  <si>
+    <t>13_2_2</t>
+  </si>
+  <si>
+    <t>Oportunidad de la notificación de IAD individual</t>
+  </si>
+  <si>
+    <t>13_2_3</t>
+  </si>
+  <si>
+    <t>Revisar la calidad del dato notificado para los casos IAD individual</t>
+  </si>
+  <si>
+    <t>13_2_4</t>
+  </si>
+  <si>
+    <t>Revisar la caracterización de las UPGDS en el SIVIGILA</t>
+  </si>
+  <si>
+    <t>13_2_5</t>
+  </si>
+  <si>
+    <t>Revisar incidencia en calidad de dato de la notificación  individual y colectiva de IAD, generando informe a la subred.</t>
+  </si>
+  <si>
+    <t>13_3_1</t>
+  </si>
+  <si>
+    <t>Verificar que la IPS realiza la evaluación periodica del consumo de antimicrobianos en el ambito hospitalario y se encuentre documentado en acta.</t>
+  </si>
+  <si>
+    <t>13_3</t>
+  </si>
+  <si>
+    <t>CAB - Calidad en la notificación de eventos de interés en salud pública</t>
+  </si>
+  <si>
+    <t>13_3_2</t>
+  </si>
+  <si>
+    <t>Revisar calidad de dato en la notificación  colectiva de  CAB</t>
+  </si>
+  <si>
+    <t>13_3_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verificar que la Institución garantiza la realización de los ajustes necesarios al Sivigila </t>
+  </si>
+  <si>
+    <t>13_4_1</t>
+  </si>
+  <si>
+    <t>Revisar calidad de dato de la notificación individual IAPMQ</t>
+  </si>
+  <si>
+    <t>13_4</t>
+  </si>
+  <si>
+    <t>IAPMQ - Calidad en la notificación de eventos de interés en salud pública</t>
+  </si>
+  <si>
+    <t>13_4_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revisar calidad de dato de la notificación colectiva para IAPMQ,  </t>
+  </si>
+  <si>
+    <t>13_4_3</t>
+  </si>
+  <si>
+    <t>Verificar la realización de la BAI de IAPMQ en los formatos establecidos</t>
+  </si>
+  <si>
+    <t>13_5_1</t>
+  </si>
+  <si>
+    <t>Calidad de la información de RAM variables de nombre de la base, localización, muestra</t>
+  </si>
+  <si>
+    <t>13_5</t>
+  </si>
+  <si>
+    <t>RAM - Calidad en la notificación de eventos de interés en salud pública</t>
+  </si>
+  <si>
+    <t>13_5_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Calidad de la información de RAM en las variables microorganismo, dilución de los antimicrobianos.</t>
+  </si>
+  <si>
+    <t>13_5_3</t>
+  </si>
+  <si>
+    <t>Verificar Concordancia WHONET (IAD-ISO) vs Sivigila mensual</t>
+  </si>
+  <si>
+    <t>13_5_4</t>
+  </si>
+  <si>
+    <t>Análisis de perfiles microbiologicos y de resistencia a los antimicrobianos semestral</t>
+  </si>
+  <si>
+    <t>13_5_5</t>
+  </si>
+  <si>
+    <t>Envió oportuno de los ajustes solicitados a nivel distrital y nacional</t>
+  </si>
+  <si>
+    <t>13_6_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cuenta con el complemento para generacion de graficos de control </t>
+  </si>
+  <si>
+    <t>13_6</t>
+  </si>
+  <si>
+    <t>BROTES IAAS -  Calidad en la notificación de eventos de interés en salud pública</t>
+  </si>
+  <si>
+    <t>13_6_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La IPS cuenta con estrategias para identificar brotes de IAAS (identificar cuales) </t>
+  </si>
+  <si>
+    <t>13_6_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La IPS realiza análisis de tableros de incidencias de los eventos IAAS para identificar comportamientos inusuales, en servicios priorizados </t>
+  </si>
+  <si>
+    <t>13_6_4</t>
+  </si>
+  <si>
+    <t>La IPS realiza seguimiento en implementación de los paquetes de medidas para la prevención y control de las IAAS.</t>
+  </si>
+  <si>
+    <t>13_6_5</t>
+  </si>
+  <si>
+    <t>Verique la oportunidad en la notificación del brote de IAAS a la SDS</t>
+  </si>
+  <si>
+    <t>13_6_6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Si la IPS a notificado un brote de IAAS revise los informes generados, verificando que cumpla con los lineamientos distritales  </t>
+  </si>
+  <si>
+    <t>13_6_7</t>
+  </si>
+  <si>
+    <t>La IPS cuenta con los analisis de mortalidad en el marco de un brote, según lineamientos distritales</t>
+  </si>
+  <si>
+    <t>11660</t>
+  </si>
+  <si>
+    <t>11670</t>
+  </si>
+  <si>
+    <t>11680</t>
+  </si>
+  <si>
+    <t>11690</t>
+  </si>
+  <si>
+    <t>11700</t>
+  </si>
+  <si>
+    <t>11710</t>
+  </si>
+  <si>
+    <t>11720</t>
+  </si>
+  <si>
+    <t>11730</t>
+  </si>
+  <si>
+    <t>11740</t>
+  </si>
+  <si>
+    <t>11750</t>
+  </si>
+  <si>
+    <t>11760</t>
+  </si>
+  <si>
+    <t>11770</t>
+  </si>
+  <si>
+    <t>11780</t>
+  </si>
+  <si>
+    <t>11790</t>
+  </si>
+  <si>
+    <t>11800</t>
+  </si>
+  <si>
+    <t>11810</t>
+  </si>
+  <si>
+    <t>11820</t>
+  </si>
+  <si>
+    <t>11830</t>
+  </si>
+  <si>
+    <t>11840</t>
+  </si>
+  <si>
+    <t>11850</t>
+  </si>
+  <si>
+    <t>11860</t>
+  </si>
+  <si>
+    <t>11870</t>
+  </si>
+  <si>
+    <t>11880</t>
+  </si>
+  <si>
+    <t>11890</t>
+  </si>
+  <si>
+    <t>11900</t>
+  </si>
+  <si>
+    <t>11910</t>
+  </si>
+  <si>
+    <t>11920</t>
+  </si>
+  <si>
+    <t>11930</t>
+  </si>
+  <si>
+    <t>11940</t>
+  </si>
+  <si>
+    <t>11950</t>
+  </si>
+  <si>
+    <t>11960</t>
+  </si>
+  <si>
+    <t>11970</t>
+  </si>
+  <si>
+    <t>11980</t>
+  </si>
+  <si>
+    <t>11990</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1761,6 +2106,12 @@
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -2090,8 +2441,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{80F83481-E46E-43DE-9D95-422AF1A554D6}" name="Dim_Componentes_SVSP" displayName="Dim_Componentes_SVSP" ref="A1:I166" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9">
-  <autoFilter ref="A1:I166" xr:uid="{80F83481-E46E-43DE-9D95-422AF1A554D6}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{80F83481-E46E-43DE-9D95-422AF1A554D6}" name="Dim_Componentes_SVSP" displayName="Dim_Componentes_SVSP" ref="A1:I200" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9">
+  <autoFilter ref="A1:I200" xr:uid="{80F83481-E46E-43DE-9D95-422AF1A554D6}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{B1A27102-7B7B-4FB0-8CDC-B37FBE546E73}" name="Id_Global" dataDxfId="8"/>
     <tableColumn id="2" xr3:uid="{47BE095A-2C44-4FFF-9A17-D8E645121C23}" name="Id_Componente" dataDxfId="7"/>
@@ -2425,7 +2776,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E66AA81A-5A75-47AB-8449-EABA6F85A7A5}">
   <sheetPr codeName="Hoja2"/>
-  <dimension ref="A1:I166"/>
+  <dimension ref="A1:I200"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.33203125" style="10" customWidth="1"/>
@@ -7254,7 +7605,994 @@
         <v>495</v>
       </c>
     </row>
+    <row r="167" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A167" s="6" t="s">
+        <v>637</v>
+      </c>
+      <c r="B167" s="7" t="s">
+        <v>556</v>
+      </c>
+      <c r="C167" s="8" t="s">
+        <v>557</v>
+      </c>
+      <c r="D167" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E167" s="6">
+        <v>3.4</v>
+      </c>
+      <c r="F167" s="6" t="s">
+        <v>558</v>
+      </c>
+      <c r="G167" s="9" t="s">
+        <v>559</v>
+      </c>
+      <c r="H167" s="6">
+        <v>13</v>
+      </c>
+      <c r="I167" s="6" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="168" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A168" s="6" t="s">
+        <v>638</v>
+      </c>
+      <c r="B168" s="7" t="s">
+        <v>561</v>
+      </c>
+      <c r="C168" s="8" t="s">
+        <v>562</v>
+      </c>
+      <c r="D168" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E168" s="6">
+        <v>4.5</v>
+      </c>
+      <c r="F168" s="6" t="s">
+        <v>558</v>
+      </c>
+      <c r="G168" s="9" t="s">
+        <v>559</v>
+      </c>
+      <c r="H168" s="6">
+        <v>13</v>
+      </c>
+      <c r="I168" s="6" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="169" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A169" s="6" t="s">
+        <v>639</v>
+      </c>
+      <c r="B169" s="7" t="s">
+        <v>563</v>
+      </c>
+      <c r="C169" s="8" t="s">
+        <v>564</v>
+      </c>
+      <c r="D169" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E169" s="6">
+        <v>2.7</v>
+      </c>
+      <c r="F169" s="6" t="s">
+        <v>558</v>
+      </c>
+      <c r="G169" s="9" t="s">
+        <v>559</v>
+      </c>
+      <c r="H169" s="6">
+        <v>13</v>
+      </c>
+      <c r="I169" s="6" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="170" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A170" s="6" t="s">
+        <v>640</v>
+      </c>
+      <c r="B170" s="7" t="s">
+        <v>565</v>
+      </c>
+      <c r="C170" s="8" t="s">
+        <v>566</v>
+      </c>
+      <c r="D170" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E170" s="6">
+        <v>2.6</v>
+      </c>
+      <c r="F170" s="6" t="s">
+        <v>558</v>
+      </c>
+      <c r="G170" s="9" t="s">
+        <v>559</v>
+      </c>
+      <c r="H170" s="6">
+        <v>13</v>
+      </c>
+      <c r="I170" s="6" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="171" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A171" s="6" t="s">
+        <v>641</v>
+      </c>
+      <c r="B171" s="7" t="s">
+        <v>567</v>
+      </c>
+      <c r="C171" s="8" t="s">
+        <v>568</v>
+      </c>
+      <c r="D171" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="E171" s="6">
+        <v>2.6</v>
+      </c>
+      <c r="F171" s="6" t="s">
+        <v>558</v>
+      </c>
+      <c r="G171" s="9" t="s">
+        <v>559</v>
+      </c>
+      <c r="H171" s="6">
+        <v>13</v>
+      </c>
+      <c r="I171" s="6" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="172" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A172" s="6" t="s">
+        <v>642</v>
+      </c>
+      <c r="B172" s="7" t="s">
+        <v>569</v>
+      </c>
+      <c r="C172" s="8" t="s">
+        <v>570</v>
+      </c>
+      <c r="D172" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="E172" s="6">
+        <v>5</v>
+      </c>
+      <c r="F172" s="6" t="s">
+        <v>558</v>
+      </c>
+      <c r="G172" s="9" t="s">
+        <v>559</v>
+      </c>
+      <c r="H172" s="6">
+        <v>13</v>
+      </c>
+      <c r="I172" s="6" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="173" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A173" s="6" t="s">
+        <v>643</v>
+      </c>
+      <c r="B173" s="7" t="s">
+        <v>571</v>
+      </c>
+      <c r="C173" s="8" t="s">
+        <v>572</v>
+      </c>
+      <c r="D173" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="E173" s="6">
+        <v>5</v>
+      </c>
+      <c r="F173" s="6" t="s">
+        <v>558</v>
+      </c>
+      <c r="G173" s="9" t="s">
+        <v>559</v>
+      </c>
+      <c r="H173" s="6">
+        <v>13</v>
+      </c>
+      <c r="I173" s="6" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="174" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A174" s="6" t="s">
+        <v>644</v>
+      </c>
+      <c r="B174" s="7" t="s">
+        <v>573</v>
+      </c>
+      <c r="C174" s="8" t="s">
+        <v>574</v>
+      </c>
+      <c r="D174" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="E174" s="6">
+        <v>3</v>
+      </c>
+      <c r="F174" s="6" t="s">
+        <v>558</v>
+      </c>
+      <c r="G174" s="9" t="s">
+        <v>559</v>
+      </c>
+      <c r="H174" s="6">
+        <v>13</v>
+      </c>
+      <c r="I174" s="6" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="175" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A175" s="6" t="s">
+        <v>645</v>
+      </c>
+      <c r="B175" s="7" t="s">
+        <v>575</v>
+      </c>
+      <c r="C175" s="8" t="s">
+        <v>576</v>
+      </c>
+      <c r="D175" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="E175" s="6">
+        <v>2.6</v>
+      </c>
+      <c r="F175" s="6" t="s">
+        <v>558</v>
+      </c>
+      <c r="G175" s="9" t="s">
+        <v>559</v>
+      </c>
+      <c r="H175" s="6">
+        <v>13</v>
+      </c>
+      <c r="I175" s="6" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="176" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A176" s="6" t="s">
+        <v>646</v>
+      </c>
+      <c r="B176" s="7" t="s">
+        <v>577</v>
+      </c>
+      <c r="C176" s="8" t="s">
+        <v>578</v>
+      </c>
+      <c r="D176" s="6">
+        <v>10</v>
+      </c>
+      <c r="E176" s="6">
+        <v>3</v>
+      </c>
+      <c r="F176" s="6" t="s">
+        <v>558</v>
+      </c>
+      <c r="G176" s="9" t="s">
+        <v>559</v>
+      </c>
+      <c r="H176" s="6">
+        <v>13</v>
+      </c>
+      <c r="I176" s="6" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="177" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A177" s="6" t="s">
+        <v>647</v>
+      </c>
+      <c r="B177" s="7" t="s">
+        <v>579</v>
+      </c>
+      <c r="C177" s="8" t="s">
+        <v>580</v>
+      </c>
+      <c r="D177" s="6">
+        <v>11</v>
+      </c>
+      <c r="E177" s="6">
+        <v>3</v>
+      </c>
+      <c r="F177" s="6" t="s">
+        <v>558</v>
+      </c>
+      <c r="G177" s="9" t="s">
+        <v>559</v>
+      </c>
+      <c r="H177" s="6">
+        <v>13</v>
+      </c>
+      <c r="I177" s="6" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="178" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A178" s="6" t="s">
+        <v>648</v>
+      </c>
+      <c r="B178" s="7" t="s">
+        <v>581</v>
+      </c>
+      <c r="C178" s="8" t="s">
+        <v>582</v>
+      </c>
+      <c r="D178" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E178" s="6">
+        <v>2.6</v>
+      </c>
+      <c r="F178" s="6" t="s">
+        <v>583</v>
+      </c>
+      <c r="G178" s="9" t="s">
+        <v>584</v>
+      </c>
+      <c r="H178" s="6">
+        <v>13</v>
+      </c>
+      <c r="I178" s="6" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="179" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A179" s="6" t="s">
+        <v>649</v>
+      </c>
+      <c r="B179" s="7" t="s">
+        <v>585</v>
+      </c>
+      <c r="C179" s="8" t="s">
+        <v>586</v>
+      </c>
+      <c r="D179" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E179" s="6">
+        <v>2.6</v>
+      </c>
+      <c r="F179" s="6" t="s">
+        <v>583</v>
+      </c>
+      <c r="G179" s="9" t="s">
+        <v>584</v>
+      </c>
+      <c r="H179" s="6">
+        <v>13</v>
+      </c>
+      <c r="I179" s="6" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="180" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A180" s="6" t="s">
+        <v>650</v>
+      </c>
+      <c r="B180" s="7" t="s">
+        <v>587</v>
+      </c>
+      <c r="C180" s="8" t="s">
+        <v>588</v>
+      </c>
+      <c r="D180" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E180" s="6">
+        <v>2.6</v>
+      </c>
+      <c r="F180" s="6" t="s">
+        <v>583</v>
+      </c>
+      <c r="G180" s="9" t="s">
+        <v>584</v>
+      </c>
+      <c r="H180" s="6">
+        <v>13</v>
+      </c>
+      <c r="I180" s="6" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="181" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A181" s="6" t="s">
+        <v>651</v>
+      </c>
+      <c r="B181" s="7" t="s">
+        <v>589</v>
+      </c>
+      <c r="C181" s="8" t="s">
+        <v>590</v>
+      </c>
+      <c r="D181" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E181" s="6">
+        <v>3.5</v>
+      </c>
+      <c r="F181" s="6" t="s">
+        <v>583</v>
+      </c>
+      <c r="G181" s="9" t="s">
+        <v>584</v>
+      </c>
+      <c r="H181" s="6">
+        <v>13</v>
+      </c>
+      <c r="I181" s="6" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="182" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A182" s="6" t="s">
+        <v>652</v>
+      </c>
+      <c r="B182" s="7" t="s">
+        <v>591</v>
+      </c>
+      <c r="C182" s="8" t="s">
+        <v>592</v>
+      </c>
+      <c r="D182" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="E182" s="6">
+        <v>1</v>
+      </c>
+      <c r="F182" s="6" t="s">
+        <v>583</v>
+      </c>
+      <c r="G182" s="9" t="s">
+        <v>584</v>
+      </c>
+      <c r="H182" s="6">
+        <v>13</v>
+      </c>
+      <c r="I182" s="6" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="183" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A183" s="6" t="s">
+        <v>653</v>
+      </c>
+      <c r="B183" s="7" t="s">
+        <v>593</v>
+      </c>
+      <c r="C183" s="8" t="s">
+        <v>594</v>
+      </c>
+      <c r="D183" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E183" s="6">
+        <v>3</v>
+      </c>
+      <c r="F183" s="6" t="s">
+        <v>595</v>
+      </c>
+      <c r="G183" s="9" t="s">
+        <v>596</v>
+      </c>
+      <c r="H183" s="6">
+        <v>13</v>
+      </c>
+      <c r="I183" s="6" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="184" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A184" s="6" t="s">
+        <v>654</v>
+      </c>
+      <c r="B184" s="7" t="s">
+        <v>597</v>
+      </c>
+      <c r="C184" s="8" t="s">
+        <v>598</v>
+      </c>
+      <c r="D184" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E184" s="6">
+        <v>3</v>
+      </c>
+      <c r="F184" s="6" t="s">
+        <v>595</v>
+      </c>
+      <c r="G184" s="9" t="s">
+        <v>596</v>
+      </c>
+      <c r="H184" s="6">
+        <v>13</v>
+      </c>
+      <c r="I184" s="6" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="185" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A185" s="6" t="s">
+        <v>655</v>
+      </c>
+      <c r="B185" s="7" t="s">
+        <v>599</v>
+      </c>
+      <c r="C185" s="8" t="s">
+        <v>600</v>
+      </c>
+      <c r="D185" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E185" s="6">
+        <v>2.6</v>
+      </c>
+      <c r="F185" s="6" t="s">
+        <v>595</v>
+      </c>
+      <c r="G185" s="9" t="s">
+        <v>596</v>
+      </c>
+      <c r="H185" s="6">
+        <v>13</v>
+      </c>
+      <c r="I185" s="6" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="186" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A186" s="6" t="s">
+        <v>656</v>
+      </c>
+      <c r="B186" s="7" t="s">
+        <v>601</v>
+      </c>
+      <c r="C186" s="8" t="s">
+        <v>602</v>
+      </c>
+      <c r="D186" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E186" s="6">
+        <v>2.6</v>
+      </c>
+      <c r="F186" s="6" t="s">
+        <v>603</v>
+      </c>
+      <c r="G186" s="9" t="s">
+        <v>604</v>
+      </c>
+      <c r="H186" s="6">
+        <v>13</v>
+      </c>
+      <c r="I186" s="6" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="187" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A187" s="6" t="s">
+        <v>657</v>
+      </c>
+      <c r="B187" s="7" t="s">
+        <v>605</v>
+      </c>
+      <c r="C187" s="8" t="s">
+        <v>606</v>
+      </c>
+      <c r="D187" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E187" s="6">
+        <v>2.6</v>
+      </c>
+      <c r="F187" s="6" t="s">
+        <v>603</v>
+      </c>
+      <c r="G187" s="9" t="s">
+        <v>604</v>
+      </c>
+      <c r="H187" s="6">
+        <v>13</v>
+      </c>
+      <c r="I187" s="6" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="188" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A188" s="6" t="s">
+        <v>658</v>
+      </c>
+      <c r="B188" s="7" t="s">
+        <v>607</v>
+      </c>
+      <c r="C188" s="8" t="s">
+        <v>608</v>
+      </c>
+      <c r="D188" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E188" s="6">
+        <v>2.6</v>
+      </c>
+      <c r="F188" s="6" t="s">
+        <v>603</v>
+      </c>
+      <c r="G188" s="9" t="s">
+        <v>604</v>
+      </c>
+      <c r="H188" s="6">
+        <v>13</v>
+      </c>
+      <c r="I188" s="6" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="189" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A189" s="6" t="s">
+        <v>659</v>
+      </c>
+      <c r="B189" s="7" t="s">
+        <v>609</v>
+      </c>
+      <c r="C189" s="8" t="s">
+        <v>610</v>
+      </c>
+      <c r="D189" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E189" s="6">
+        <v>2.7</v>
+      </c>
+      <c r="F189" s="6" t="s">
+        <v>611</v>
+      </c>
+      <c r="G189" s="9" t="s">
+        <v>612</v>
+      </c>
+      <c r="H189" s="6">
+        <v>13</v>
+      </c>
+      <c r="I189" s="6" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="190" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A190" s="6" t="s">
+        <v>660</v>
+      </c>
+      <c r="B190" s="7" t="s">
+        <v>613</v>
+      </c>
+      <c r="C190" s="8" t="s">
+        <v>614</v>
+      </c>
+      <c r="D190" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E190" s="6">
+        <v>2.7</v>
+      </c>
+      <c r="F190" s="6" t="s">
+        <v>611</v>
+      </c>
+      <c r="G190" s="9" t="s">
+        <v>612</v>
+      </c>
+      <c r="H190" s="6">
+        <v>13</v>
+      </c>
+      <c r="I190" s="6" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="191" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A191" s="6" t="s">
+        <v>661</v>
+      </c>
+      <c r="B191" s="7" t="s">
+        <v>615</v>
+      </c>
+      <c r="C191" s="8" t="s">
+        <v>616</v>
+      </c>
+      <c r="D191" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E191" s="6">
+        <v>2.7</v>
+      </c>
+      <c r="F191" s="6" t="s">
+        <v>611</v>
+      </c>
+      <c r="G191" s="9" t="s">
+        <v>612</v>
+      </c>
+      <c r="H191" s="6">
+        <v>13</v>
+      </c>
+      <c r="I191" s="6" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="192" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A192" s="6" t="s">
+        <v>662</v>
+      </c>
+      <c r="B192" s="7" t="s">
+        <v>617</v>
+      </c>
+      <c r="C192" s="8" t="s">
+        <v>618</v>
+      </c>
+      <c r="D192" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E192" s="6">
+        <v>3</v>
+      </c>
+      <c r="F192" s="6" t="s">
+        <v>611</v>
+      </c>
+      <c r="G192" s="9" t="s">
+        <v>612</v>
+      </c>
+      <c r="H192" s="6">
+        <v>13</v>
+      </c>
+      <c r="I192" s="6" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="193" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A193" s="6" t="s">
+        <v>663</v>
+      </c>
+      <c r="B193" s="7" t="s">
+        <v>619</v>
+      </c>
+      <c r="C193" s="8" t="s">
+        <v>620</v>
+      </c>
+      <c r="D193" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="E193" s="6">
+        <v>2.6</v>
+      </c>
+      <c r="F193" s="6" t="s">
+        <v>611</v>
+      </c>
+      <c r="G193" s="9" t="s">
+        <v>612</v>
+      </c>
+      <c r="H193" s="6">
+        <v>13</v>
+      </c>
+      <c r="I193" s="6" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="194" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A194" s="6" t="s">
+        <v>664</v>
+      </c>
+      <c r="B194" s="7" t="s">
+        <v>621</v>
+      </c>
+      <c r="C194" s="8" t="s">
+        <v>622</v>
+      </c>
+      <c r="D194" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E194" s="6">
+        <v>2.7</v>
+      </c>
+      <c r="F194" s="6" t="s">
+        <v>623</v>
+      </c>
+      <c r="G194" s="9" t="s">
+        <v>624</v>
+      </c>
+      <c r="H194" s="6">
+        <v>13</v>
+      </c>
+      <c r="I194" s="6" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="195" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A195" s="6" t="s">
+        <v>665</v>
+      </c>
+      <c r="B195" s="7" t="s">
+        <v>625</v>
+      </c>
+      <c r="C195" s="8" t="s">
+        <v>626</v>
+      </c>
+      <c r="D195" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E195" s="6">
+        <v>4</v>
+      </c>
+      <c r="F195" s="6" t="s">
+        <v>623</v>
+      </c>
+      <c r="G195" s="9" t="s">
+        <v>624</v>
+      </c>
+      <c r="H195" s="6">
+        <v>13</v>
+      </c>
+      <c r="I195" s="6" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="196" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A196" s="6" t="s">
+        <v>666</v>
+      </c>
+      <c r="B196" s="7" t="s">
+        <v>627</v>
+      </c>
+      <c r="C196" s="8" t="s">
+        <v>628</v>
+      </c>
+      <c r="D196" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E196" s="6">
+        <v>2.7</v>
+      </c>
+      <c r="F196" s="6" t="s">
+        <v>623</v>
+      </c>
+      <c r="G196" s="9" t="s">
+        <v>624</v>
+      </c>
+      <c r="H196" s="6">
+        <v>13</v>
+      </c>
+      <c r="I196" s="6" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="197" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A197" s="6" t="s">
+        <v>667</v>
+      </c>
+      <c r="B197" s="7" t="s">
+        <v>629</v>
+      </c>
+      <c r="C197" s="8" t="s">
+        <v>630</v>
+      </c>
+      <c r="D197" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E197" s="6">
+        <v>2.7</v>
+      </c>
+      <c r="F197" s="6" t="s">
+        <v>623</v>
+      </c>
+      <c r="G197" s="9" t="s">
+        <v>624</v>
+      </c>
+      <c r="H197" s="6">
+        <v>13</v>
+      </c>
+      <c r="I197" s="6" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="198" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A198" s="6" t="s">
+        <v>668</v>
+      </c>
+      <c r="B198" s="7" t="s">
+        <v>631</v>
+      </c>
+      <c r="C198" s="8" t="s">
+        <v>632</v>
+      </c>
+      <c r="D198" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="E198" s="6">
+        <v>2.7</v>
+      </c>
+      <c r="F198" s="6" t="s">
+        <v>623</v>
+      </c>
+      <c r="G198" s="9" t="s">
+        <v>624</v>
+      </c>
+      <c r="H198" s="6">
+        <v>13</v>
+      </c>
+      <c r="I198" s="6" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="199" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A199" s="6" t="s">
+        <v>669</v>
+      </c>
+      <c r="B199" s="7" t="s">
+        <v>633</v>
+      </c>
+      <c r="C199" s="8" t="s">
+        <v>634</v>
+      </c>
+      <c r="D199" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="E199" s="6">
+        <v>2.7</v>
+      </c>
+      <c r="F199" s="6" t="s">
+        <v>623</v>
+      </c>
+      <c r="G199" s="9" t="s">
+        <v>624</v>
+      </c>
+      <c r="H199" s="6">
+        <v>13</v>
+      </c>
+      <c r="I199" s="6" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="200" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A200" s="6" t="s">
+        <v>670</v>
+      </c>
+      <c r="B200" s="7" t="s">
+        <v>635</v>
+      </c>
+      <c r="C200" s="8" t="s">
+        <v>636</v>
+      </c>
+      <c r="D200" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="E200" s="6">
+        <v>2.7</v>
+      </c>
+      <c r="F200" s="6" t="s">
+        <v>623</v>
+      </c>
+      <c r="G200" s="9" t="s">
+        <v>624</v>
+      </c>
+      <c r="H200" s="6">
+        <v>13</v>
+      </c>
+      <c r="I200" s="6" t="s">
+        <v>560</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
